--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2050,6 +2050,714 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122310983</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sandtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>697700</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6556781</v>
+      </c>
+      <c r="S14" t="n">
+        <v>21</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122311010</v>
+      </c>
+      <c r="B15" t="n">
+        <v>110296</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sandtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>697679</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6556777</v>
+      </c>
+      <c r="S15" t="n">
+        <v>11</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122309800</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8436</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sandtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>697596</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6557005</v>
+      </c>
+      <c r="S16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122310585</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90783</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sandtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>697618</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6556920</v>
+      </c>
+      <c r="S17" t="n">
+        <v>41</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122311404</v>
+      </c>
+      <c r="B18" t="n">
+        <v>110296</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hemträsket, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>697695</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6556744</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122310912</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100425</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sandtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>697686</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6556802</v>
+      </c>
+      <c r="S19" t="n">
+        <v>24</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122310983</v>
+        <v>122311404</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
+        <v>110296</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,49 +2064,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697700</v>
+        <v>697695</v>
       </c>
       <c r="R14" t="n">
-        <v>6556781</v>
+        <v>6556744</v>
       </c>
       <c r="S14" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2135,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2288,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122309800</v>
+        <v>122310983</v>
       </c>
       <c r="B16" t="n">
-        <v>8436</v>
+        <v>57390</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,25 +2296,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2326,7 +2322,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -2337,13 +2332,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697596</v>
+        <v>697700</v>
       </c>
       <c r="R16" t="n">
-        <v>6557005</v>
+        <v>6556781</v>
       </c>
       <c r="S16" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2372,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2528,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122311404</v>
+        <v>122310912</v>
       </c>
       <c r="B18" t="n">
-        <v>110296</v>
+        <v>100425</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,21 +2539,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2568,17 +2563,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697695</v>
+        <v>697686</v>
       </c>
       <c r="R18" t="n">
-        <v>6556744</v>
+        <v>6556802</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2607,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2612,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,10 +2639,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122310912</v>
+        <v>122309800</v>
       </c>
       <c r="B19" t="n">
-        <v>100425</v>
+        <v>8436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,27 +2655,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697686</v>
+        <v>697596</v>
       </c>
       <c r="R19" t="n">
-        <v>6556802</v>
+        <v>6557005</v>
       </c>
       <c r="S19" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,6 +2757,678 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122324705</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90783</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>697615</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6556966</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122324459</v>
+      </c>
+      <c r="B21" t="n">
+        <v>94931</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>697641</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6556847</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122323126</v>
+      </c>
+      <c r="B22" t="n">
+        <v>110296</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hemträsket, Hemträsket, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>697732</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6556749</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122323928</v>
+      </c>
+      <c r="B23" t="n">
+        <v>110296</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hemträsket, Hemträsket, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>697678</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6556740</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122323737</v>
+      </c>
+      <c r="B24" t="n">
+        <v>110296</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hemträsket, Hemträsket, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>697676</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6556742</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122323326</v>
+      </c>
+      <c r="B25" t="n">
+        <v>110296</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hemträsket, Hemträsket, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>697701</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6556732</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2171,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122311404</v>
+        <v>122309800</v>
       </c>
       <c r="B15" t="n">
-        <v>110312</v>
+        <v>8436</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,41 +2187,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697695</v>
+        <v>697596</v>
       </c>
       <c r="R15" t="n">
-        <v>6556744</v>
+        <v>6557005</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2250,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122310912</v>
+        <v>122311010</v>
       </c>
       <c r="B16" t="n">
-        <v>100441</v>
+        <v>110312</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,21 +2308,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2331,13 +2336,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697686</v>
+        <v>697679</v>
       </c>
       <c r="R16" t="n">
-        <v>6556802</v>
+        <v>6556777</v>
       </c>
       <c r="S16" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2366,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,7 +2408,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122311010</v>
+        <v>122311404</v>
       </c>
       <c r="B17" t="n">
         <v>110312</v>
@@ -2443,14 +2448,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697679</v>
+        <v>697695</v>
       </c>
       <c r="R17" t="n">
-        <v>6556777</v>
+        <v>6556744</v>
       </c>
       <c r="S17" t="n">
         <v>11</v>
@@ -2482,7 +2487,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2497,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122309800</v>
+        <v>122310912</v>
       </c>
       <c r="B18" t="n">
-        <v>8436</v>
+        <v>100441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,32 +2540,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697596</v>
+        <v>697686</v>
       </c>
       <c r="R18" t="n">
-        <v>6557005</v>
+        <v>6556802</v>
       </c>
       <c r="S18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122323326</v>
+        <v>122324705</v>
       </c>
       <c r="B20" t="n">
-        <v>110312</v>
+        <v>90799</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,41 +2772,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697701</v>
+        <v>697615</v>
       </c>
       <c r="R20" t="n">
-        <v>6556732</v>
+        <v>6556966</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122324459</v>
+        <v>122323326</v>
       </c>
       <c r="B21" t="n">
-        <v>94947</v>
+        <v>110312</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2888,34 +2888,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697641</v>
+        <v>697701</v>
       </c>
       <c r="R21" t="n">
-        <v>6556847</v>
+        <v>6556732</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,7 +2984,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122323737</v>
+        <v>122323126</v>
       </c>
       <c r="B22" t="n">
         <v>110312</v>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697676</v>
+        <v>697732</v>
       </c>
       <c r="R22" t="n">
-        <v>6556742</v>
+        <v>6556749</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122324705</v>
+        <v>122323737</v>
       </c>
       <c r="B23" t="n">
-        <v>90799</v>
+        <v>110312</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3108,41 +3108,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697615</v>
+        <v>697676</v>
       </c>
       <c r="R23" t="n">
-        <v>6556966</v>
+        <v>6556742</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122323928</v>
+        <v>122324459</v>
       </c>
       <c r="B24" t="n">
-        <v>110312</v>
+        <v>94947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,34 +3224,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697678</v>
+        <v>697641</v>
       </c>
       <c r="R24" t="n">
-        <v>6556740</v>
+        <v>6556847</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122323126</v>
+        <v>122323928</v>
       </c>
       <c r="B25" t="n">
         <v>110312</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697732</v>
+        <v>697678</v>
       </c>
       <c r="R25" t="n">
-        <v>6556749</v>
+        <v>6556740</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2055,7 +2055,7 @@
         <v>122310585</v>
       </c>
       <c r="B14" t="n">
-        <v>90799</v>
+        <v>90809</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122311010</v>
+        <v>122310983</v>
       </c>
       <c r="B16" t="n">
-        <v>110312</v>
+        <v>57390</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,31 +2304,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2336,13 +2340,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697679</v>
+        <v>697700</v>
       </c>
       <c r="R16" t="n">
-        <v>6556777</v>
+        <v>6556781</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2371,7 +2375,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2385,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122311404</v>
+        <v>122310912</v>
       </c>
       <c r="B17" t="n">
-        <v>110312</v>
+        <v>100451</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,21 +2428,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2448,17 +2452,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697695</v>
+        <v>697686</v>
       </c>
       <c r="R17" t="n">
-        <v>6556744</v>
+        <v>6556802</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2487,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2497,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,10 +2528,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122310912</v>
+        <v>122311010</v>
       </c>
       <c r="B18" t="n">
-        <v>100441</v>
+        <v>110322</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2540,21 +2544,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2568,13 +2572,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697686</v>
+        <v>697679</v>
       </c>
       <c r="R18" t="n">
-        <v>6556802</v>
+        <v>6556777</v>
       </c>
       <c r="S18" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122310983</v>
+        <v>122311404</v>
       </c>
       <c r="B19" t="n">
-        <v>57390</v>
+        <v>110322</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,49 +2656,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697700</v>
+        <v>697695</v>
       </c>
       <c r="R19" t="n">
-        <v>6556781</v>
+        <v>6556744</v>
       </c>
       <c r="S19" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122324705</v>
+        <v>122323737</v>
       </c>
       <c r="B20" t="n">
-        <v>90799</v>
+        <v>110322</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,41 +2772,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697615</v>
+        <v>697676</v>
       </c>
       <c r="R20" t="n">
-        <v>6556966</v>
+        <v>6556742</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>122323326</v>
       </c>
       <c r="B21" t="n">
-        <v>110312</v>
+        <v>110322</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122323126</v>
+        <v>122324459</v>
       </c>
       <c r="B22" t="n">
-        <v>110312</v>
+        <v>94957</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,34 +3000,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697732</v>
+        <v>697641</v>
       </c>
       <c r="R22" t="n">
-        <v>6556749</v>
+        <v>6556847</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122323737</v>
+        <v>122323126</v>
       </c>
       <c r="B23" t="n">
-        <v>110312</v>
+        <v>110322</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697676</v>
+        <v>697732</v>
       </c>
       <c r="R23" t="n">
-        <v>6556742</v>
+        <v>6556749</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122324459</v>
+        <v>122323928</v>
       </c>
       <c r="B24" t="n">
-        <v>94947</v>
+        <v>110322</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,34 +3224,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697641</v>
+        <v>697678</v>
       </c>
       <c r="R24" t="n">
-        <v>6556847</v>
+        <v>6556740</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122323928</v>
+        <v>122324705</v>
       </c>
       <c r="B25" t="n">
-        <v>110312</v>
+        <v>90809</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,41 +3332,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697678</v>
+        <v>697615</v>
       </c>
       <c r="R25" t="n">
-        <v>6556740</v>
+        <v>6556966</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122310585</v>
+        <v>122310983</v>
       </c>
       <c r="B14" t="n">
-        <v>90809</v>
+        <v>57390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2090,8 +2090,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2099,13 +2100,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697618</v>
+        <v>697700</v>
       </c>
       <c r="R14" t="n">
-        <v>6556920</v>
+        <v>6556781</v>
       </c>
       <c r="S14" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122309800</v>
+        <v>122310585</v>
       </c>
       <c r="B15" t="n">
-        <v>8436</v>
+        <v>90809</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,25 +2184,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2211,8 +2212,6 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2220,13 +2219,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697596</v>
+        <v>697618</v>
       </c>
       <c r="R15" t="n">
-        <v>6557005</v>
+        <v>6556920</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2255,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122310983</v>
+        <v>122311404</v>
       </c>
       <c r="B16" t="n">
-        <v>57390</v>
+        <v>110322</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,49 +2303,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697700</v>
+        <v>697695</v>
       </c>
       <c r="R16" t="n">
-        <v>6556781</v>
+        <v>6556744</v>
       </c>
       <c r="S16" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2375,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2385,7 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2412,10 +2407,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122310912</v>
+        <v>122309800</v>
       </c>
       <c r="B17" t="n">
-        <v>100451</v>
+        <v>8436</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,27 +2423,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2456,13 +2456,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697686</v>
+        <v>697596</v>
       </c>
       <c r="R17" t="n">
-        <v>6556802</v>
+        <v>6557005</v>
       </c>
       <c r="S17" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2528,10 +2528,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122311010</v>
+        <v>122310912</v>
       </c>
       <c r="B18" t="n">
-        <v>110322</v>
+        <v>100451</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697679</v>
+        <v>697686</v>
       </c>
       <c r="R18" t="n">
-        <v>6556777</v>
+        <v>6556802</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,7 +2644,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122311404</v>
+        <v>122311010</v>
       </c>
       <c r="B19" t="n">
         <v>110322</v>
@@ -2684,14 +2684,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697695</v>
+        <v>697679</v>
       </c>
       <c r="R19" t="n">
-        <v>6556744</v>
+        <v>6556777</v>
       </c>
       <c r="S19" t="n">
         <v>11</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122323737</v>
+        <v>122324705</v>
       </c>
       <c r="B20" t="n">
-        <v>110322</v>
+        <v>90809</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,41 +2772,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697676</v>
+        <v>697615</v>
       </c>
       <c r="R20" t="n">
-        <v>6556742</v>
+        <v>6556966</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122323326</v>
+        <v>122323737</v>
       </c>
       <c r="B21" t="n">
         <v>110322</v>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697701</v>
+        <v>697676</v>
       </c>
       <c r="R21" t="n">
-        <v>6556732</v>
+        <v>6556742</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122324705</v>
+        <v>122323326</v>
       </c>
       <c r="B25" t="n">
-        <v>90809</v>
+        <v>110322</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,41 +3332,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697615</v>
+        <v>697701</v>
       </c>
       <c r="R25" t="n">
-        <v>6556966</v>
+        <v>6556732</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3429,6 +3429,112 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122450925</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78030</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sandtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>697665</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6556750</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3430,112 +3430,6 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>122450925</v>
-      </c>
-      <c r="B26" t="n">
-        <v>78030</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Sandtäppan, Srm</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>697665</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6556750</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Ornö</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-01-25</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-01-25</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Emilia Blixt</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Emilia Blixt</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2055,7 +2055,7 @@
         <v>122310983</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122310585</v>
+        <v>122311404</v>
       </c>
       <c r="B15" t="n">
-        <v>90809</v>
+        <v>110335</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,48 +2184,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697618</v>
+        <v>697695</v>
       </c>
       <c r="R15" t="n">
-        <v>6556920</v>
+        <v>6556744</v>
       </c>
       <c r="S15" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2254,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122311404</v>
+        <v>122311010</v>
       </c>
       <c r="B16" t="n">
-        <v>110322</v>
+        <v>110335</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,14 +2328,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697695</v>
+        <v>697679</v>
       </c>
       <c r="R16" t="n">
-        <v>6556744</v>
+        <v>6556777</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
@@ -2370,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122309800</v>
+        <v>122310585</v>
       </c>
       <c r="B17" t="n">
-        <v>8436</v>
+        <v>90821</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,25 +2416,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2447,8 +2444,6 @@
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2456,13 +2451,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697596</v>
+        <v>697618</v>
       </c>
       <c r="R17" t="n">
-        <v>6557005</v>
+        <v>6556920</v>
       </c>
       <c r="S17" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2528,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122310912</v>
+        <v>122309800</v>
       </c>
       <c r="B18" t="n">
-        <v>100451</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,27 +2539,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697686</v>
+        <v>697596</v>
       </c>
       <c r="R18" t="n">
-        <v>6556802</v>
+        <v>6557005</v>
       </c>
       <c r="S18" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122311010</v>
+        <v>122310912</v>
       </c>
       <c r="B19" t="n">
-        <v>110322</v>
+        <v>100463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,21 +2660,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697679</v>
+        <v>697686</v>
       </c>
       <c r="R19" t="n">
-        <v>6556777</v>
+        <v>6556802</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,7 +2763,7 @@
         <v>122324705</v>
       </c>
       <c r="B20" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122323737</v>
+        <v>122323326</v>
       </c>
       <c r="B21" t="n">
-        <v>110322</v>
+        <v>110335</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697676</v>
+        <v>697701</v>
       </c>
       <c r="R21" t="n">
-        <v>6556742</v>
+        <v>6556732</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122324459</v>
+        <v>122323126</v>
       </c>
       <c r="B22" t="n">
-        <v>94957</v>
+        <v>110335</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,34 +3000,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697641</v>
+        <v>697732</v>
       </c>
       <c r="R22" t="n">
-        <v>6556847</v>
+        <v>6556749</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122323126</v>
+        <v>122323928</v>
       </c>
       <c r="B23" t="n">
-        <v>110322</v>
+        <v>110335</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697732</v>
+        <v>697678</v>
       </c>
       <c r="R23" t="n">
-        <v>6556749</v>
+        <v>6556740</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122323928</v>
+        <v>122323737</v>
       </c>
       <c r="B24" t="n">
-        <v>110322</v>
+        <v>110335</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697678</v>
+        <v>697676</v>
       </c>
       <c r="R24" t="n">
-        <v>6556740</v>
+        <v>6556742</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122323326</v>
+        <v>122324459</v>
       </c>
       <c r="B25" t="n">
-        <v>110322</v>
+        <v>94969</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,34 +3336,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697701</v>
+        <v>697641</v>
       </c>
       <c r="R25" t="n">
-        <v>6556732</v>
+        <v>6556847</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122310983</v>
+        <v>122310912</v>
       </c>
       <c r="B14" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,35 +2064,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2100,13 +2096,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697700</v>
+        <v>697686</v>
       </c>
       <c r="R14" t="n">
-        <v>6556781</v>
+        <v>6556802</v>
       </c>
       <c r="S14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2135,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122311404</v>
+        <v>122310983</v>
       </c>
       <c r="B15" t="n">
-        <v>110335</v>
+        <v>57395</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,45 +2180,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697695</v>
+        <v>697700</v>
       </c>
       <c r="R15" t="n">
-        <v>6556744</v>
+        <v>6556781</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122311010</v>
+        <v>122309800</v>
       </c>
       <c r="B16" t="n">
-        <v>110335</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,27 +2304,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2332,13 +2337,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697679</v>
+        <v>697596</v>
       </c>
       <c r="R16" t="n">
-        <v>6556777</v>
+        <v>6557005</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122310585</v>
+        <v>122311404</v>
       </c>
       <c r="B17" t="n">
-        <v>90821</v>
+        <v>110340</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,48 +2421,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697618</v>
+        <v>697695</v>
       </c>
       <c r="R17" t="n">
-        <v>6556920</v>
+        <v>6556744</v>
       </c>
       <c r="S17" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,7 +2488,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2498,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122309800</v>
+        <v>122310585</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>90828</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,25 +2537,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2563,8 +2565,6 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697596</v>
+        <v>697618</v>
       </c>
       <c r="R18" t="n">
-        <v>6557005</v>
+        <v>6556920</v>
       </c>
       <c r="S18" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122310912</v>
+        <v>122311010</v>
       </c>
       <c r="B19" t="n">
-        <v>100463</v>
+        <v>110340</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,21 +2660,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697686</v>
+        <v>697679</v>
       </c>
       <c r="R19" t="n">
-        <v>6556802</v>
+        <v>6556777</v>
       </c>
       <c r="S19" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122324705</v>
+        <v>122323737</v>
       </c>
       <c r="B20" t="n">
-        <v>90821</v>
+        <v>110340</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,41 +2772,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697615</v>
+        <v>697676</v>
       </c>
       <c r="R20" t="n">
-        <v>6556966</v>
+        <v>6556742</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>122323326</v>
       </c>
       <c r="B21" t="n">
-        <v>110335</v>
+        <v>110340</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122323126</v>
+        <v>122323928</v>
       </c>
       <c r="B22" t="n">
-        <v>110335</v>
+        <v>110340</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697732</v>
+        <v>697678</v>
       </c>
       <c r="R22" t="n">
-        <v>6556749</v>
+        <v>6556740</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122323928</v>
+        <v>122324459</v>
       </c>
       <c r="B23" t="n">
-        <v>110335</v>
+        <v>94974</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,34 +3112,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697678</v>
+        <v>697641</v>
       </c>
       <c r="R23" t="n">
-        <v>6556740</v>
+        <v>6556847</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122323737</v>
+        <v>122323126</v>
       </c>
       <c r="B24" t="n">
-        <v>110335</v>
+        <v>110340</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697676</v>
+        <v>697732</v>
       </c>
       <c r="R24" t="n">
-        <v>6556742</v>
+        <v>6556749</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122324459</v>
+        <v>122324705</v>
       </c>
       <c r="B25" t="n">
-        <v>94969</v>
+        <v>90828</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,25 +3332,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3360,13 +3360,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697641</v>
+        <v>697615</v>
       </c>
       <c r="R25" t="n">
-        <v>6556847</v>
+        <v>6556966</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122310912</v>
+        <v>122310983</v>
       </c>
       <c r="B14" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,31 +2064,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2096,13 +2095,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697686</v>
+        <v>697700</v>
       </c>
       <c r="R14" t="n">
-        <v>6556802</v>
+        <v>6556781</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122310983</v>
+        <v>122311404</v>
       </c>
       <c r="B15" t="n">
-        <v>57395</v>
+        <v>110349</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,49 +2179,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>219711</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697700</v>
+        <v>697695</v>
       </c>
       <c r="R15" t="n">
-        <v>6556781</v>
+        <v>6556744</v>
       </c>
       <c r="S15" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122309800</v>
+        <v>122311010</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>110349</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,32 +2294,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
+        <v>219711</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2337,13 +2317,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697596</v>
+        <v>697679</v>
       </c>
       <c r="R16" t="n">
-        <v>6557005</v>
+        <v>6556777</v>
       </c>
       <c r="S16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2372,7 +2352,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2362,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122311404</v>
+        <v>122310912</v>
       </c>
       <c r="B17" t="n">
-        <v>110340</v>
+        <v>100477</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,21 +2405,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219711</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Sårläka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2449,17 +2424,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697695</v>
+        <v>697686</v>
       </c>
       <c r="R17" t="n">
-        <v>6556744</v>
+        <v>6556802</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2488,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2498,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122310585</v>
+        <v>122309800</v>
       </c>
       <c r="B18" t="n">
-        <v>90828</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,25 +2512,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>106545</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2565,6 +2535,8 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2572,13 +2544,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697618</v>
+        <v>697596</v>
       </c>
       <c r="R18" t="n">
-        <v>6556920</v>
+        <v>6557005</v>
       </c>
       <c r="S18" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2607,7 +2579,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2589,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,10 +2616,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122311010</v>
+        <v>122310585</v>
       </c>
       <c r="B19" t="n">
-        <v>110340</v>
+        <v>90833</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2656,31 +2628,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219711</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Sårläka</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2688,13 +2658,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697679</v>
+        <v>697618</v>
       </c>
       <c r="R19" t="n">
-        <v>6556777</v>
+        <v>6556920</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2703,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122323737</v>
+        <v>122323126</v>
       </c>
       <c r="B20" t="n">
-        <v>110340</v>
+        <v>110349</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2778,11 +2748,6 @@
       <c r="E20" t="n">
         <v>219711</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sårläka</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Sanicula europaea</t>
@@ -2800,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697676</v>
+        <v>697732</v>
       </c>
       <c r="R20" t="n">
-        <v>6556742</v>
+        <v>6556749</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2835,7 +2800,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2810,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122323326</v>
+        <v>122323928</v>
       </c>
       <c r="B21" t="n">
-        <v>110340</v>
+        <v>110349</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2890,11 +2855,6 @@
       <c r="E21" t="n">
         <v>219711</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Sårläka</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Sanicula europaea</t>
@@ -2912,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697701</v>
+        <v>697678</v>
       </c>
       <c r="R21" t="n">
-        <v>6556732</v>
+        <v>6556740</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2917,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2944,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122323928</v>
+        <v>122324705</v>
       </c>
       <c r="B22" t="n">
-        <v>110340</v>
+        <v>90833</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2996,41 +2956,36 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219711</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Sårläka</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697678</v>
+        <v>697615</v>
       </c>
       <c r="R22" t="n">
-        <v>6556740</v>
+        <v>6556966</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3096,10 +3051,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122324459</v>
+        <v>122323326</v>
       </c>
       <c r="B23" t="n">
-        <v>94974</v>
+        <v>110349</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,34 +3067,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
+        <v>219711</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697641</v>
+        <v>697701</v>
       </c>
       <c r="R23" t="n">
-        <v>6556847</v>
+        <v>6556732</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3171,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122323126</v>
+        <v>122323737</v>
       </c>
       <c r="B24" t="n">
-        <v>110340</v>
+        <v>110349</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3226,11 +3176,6 @@
       <c r="E24" t="n">
         <v>219711</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Sårläka</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Sanicula europaea</t>
@@ -3248,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697732</v>
+        <v>697676</v>
       </c>
       <c r="R24" t="n">
-        <v>6556749</v>
+        <v>6556742</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3283,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3293,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122324705</v>
+        <v>122324459</v>
       </c>
       <c r="B25" t="n">
-        <v>90828</v>
+        <v>94983</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,25 +3277,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>2180</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3360,13 +3300,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697615</v>
+        <v>697641</v>
       </c>
       <c r="R25" t="n">
-        <v>6556966</v>
+        <v>6556847</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3429,6 +3369,1860 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122540895</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57395</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>697710</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6556732</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122540893</v>
+      </c>
+      <c r="B27" t="n">
+        <v>100477</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>697710</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6556732</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122540891</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>697667</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6556761</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122540883</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4776</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102306</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>697616</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6556904</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122540889</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110349</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219711</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>697668</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6556773</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122540888</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100477</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>697678</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6556802</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122540878</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8430</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>697600</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6557016</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122540890</v>
+      </c>
+      <c r="B33" t="n">
+        <v>110349</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219711</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>697667</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6556761</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122540896</v>
+      </c>
+      <c r="B34" t="n">
+        <v>110349</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219711</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>697607</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6556976</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122540886</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98233</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219862</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>697681</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6556807</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122540884</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106545</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>697609</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6556889</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122540887</v>
+      </c>
+      <c r="B37" t="n">
+        <v>110349</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219711</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>697678</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6556802</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122540897</v>
+      </c>
+      <c r="B38" t="n">
+        <v>94829</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>210</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>697581</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6556970</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122540881</v>
+      </c>
+      <c r="B39" t="n">
+        <v>94733</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2818</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>697597</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6556987</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122540885</v>
+      </c>
+      <c r="B40" t="n">
+        <v>94876</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2170</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>697628</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6556873</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122540898</v>
+      </c>
+      <c r="B41" t="n">
+        <v>94829</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>210</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>697586</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6556969</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122310983</v>
+        <v>122311404</v>
       </c>
       <c r="B14" t="n">
-        <v>57395</v>
+        <v>110362</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,44 +2064,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>219711</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697700</v>
+        <v>697695</v>
       </c>
       <c r="R14" t="n">
-        <v>6556781</v>
+        <v>6556744</v>
       </c>
       <c r="S14" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2130,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122311404</v>
+        <v>122310983</v>
       </c>
       <c r="B15" t="n">
-        <v>110349</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,40 +2180,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697695</v>
+        <v>697700</v>
       </c>
       <c r="R15" t="n">
-        <v>6556744</v>
+        <v>6556781</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2241,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122311010</v>
+        <v>122310585</v>
       </c>
       <c r="B16" t="n">
-        <v>110349</v>
+        <v>90846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,26 +2300,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>5442</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2317,13 +2335,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697679</v>
+        <v>697618</v>
       </c>
       <c r="R16" t="n">
-        <v>6556777</v>
+        <v>6556920</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2352,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,10 +2407,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122310912</v>
+        <v>122309800</v>
       </c>
       <c r="B17" t="n">
-        <v>100477</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,22 +2423,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2428,13 +2456,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697686</v>
+        <v>697596</v>
       </c>
       <c r="R17" t="n">
-        <v>6556802</v>
+        <v>6557005</v>
       </c>
       <c r="S17" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2528,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122309800</v>
+        <v>122311010</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>110362</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,27 +2544,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>219711</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2544,13 +2572,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697596</v>
+        <v>697679</v>
       </c>
       <c r="R18" t="n">
-        <v>6557005</v>
+        <v>6556777</v>
       </c>
       <c r="S18" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2579,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2589,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122310585</v>
+        <v>122310912</v>
       </c>
       <c r="B19" t="n">
-        <v>90833</v>
+        <v>100490</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2628,29 +2656,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2658,13 +2688,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697618</v>
+        <v>697686</v>
       </c>
       <c r="R19" t="n">
-        <v>6556920</v>
+        <v>6556802</v>
       </c>
       <c r="S19" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122323126</v>
+        <v>122323928</v>
       </c>
       <c r="B20" t="n">
-        <v>110349</v>
+        <v>110362</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2748,6 +2778,11 @@
       <c r="E20" t="n">
         <v>219711</v>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Sanicula europaea</t>
@@ -2765,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697732</v>
+        <v>697678</v>
       </c>
       <c r="R20" t="n">
-        <v>6556749</v>
+        <v>6556740</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2800,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2810,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122323928</v>
+        <v>122323737</v>
       </c>
       <c r="B21" t="n">
-        <v>110349</v>
+        <v>110362</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,6 +2890,11 @@
       <c r="E21" t="n">
         <v>219711</v>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Sanicula europaea</t>
@@ -2872,10 +2912,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697678</v>
+        <v>697676</v>
       </c>
       <c r="R21" t="n">
-        <v>6556740</v>
+        <v>6556742</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2944,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122324705</v>
+        <v>122323126</v>
       </c>
       <c r="B22" t="n">
-        <v>90833</v>
+        <v>110362</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,36 +2996,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>219711</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697615</v>
+        <v>697732</v>
       </c>
       <c r="R22" t="n">
-        <v>6556966</v>
+        <v>6556749</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3014,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3024,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122323326</v>
+        <v>122324705</v>
       </c>
       <c r="B23" t="n">
-        <v>110349</v>
+        <v>90846</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,36 +3108,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>5442</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697701</v>
+        <v>697615</v>
       </c>
       <c r="R23" t="n">
-        <v>6556732</v>
+        <v>6556966</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3121,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122323737</v>
+        <v>122324459</v>
       </c>
       <c r="B24" t="n">
-        <v>110349</v>
+        <v>94996</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,29 +3224,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>2180</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697676</v>
+        <v>697641</v>
       </c>
       <c r="R24" t="n">
-        <v>6556742</v>
+        <v>6556847</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3265,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122324459</v>
+        <v>122323326</v>
       </c>
       <c r="B25" t="n">
-        <v>94983</v>
+        <v>110362</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,29 +3336,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>219711</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697641</v>
+        <v>697701</v>
       </c>
       <c r="R25" t="n">
-        <v>6556847</v>
+        <v>6556732</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3335,7 +3395,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3405,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540895</v>
+        <v>122540883</v>
       </c>
       <c r="B26" t="n">
-        <v>57395</v>
+        <v>4776</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3384,26 +3444,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>102306</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3412,10 +3477,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697710</v>
+        <v>697616</v>
       </c>
       <c r="R26" t="n">
-        <v>6556732</v>
+        <v>6556904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3447,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3457,12 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,6 +3533,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3489,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540893</v>
+        <v>122540884</v>
       </c>
       <c r="B27" t="n">
-        <v>100477</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3505,29 +3585,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697710</v>
+        <v>697609</v>
       </c>
       <c r="R27" t="n">
-        <v>6556732</v>
+        <v>6556889</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3559,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3659,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3580,6 +3670,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3596,10 +3701,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540891</v>
+        <v>122540895</v>
       </c>
       <c r="B28" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,30 +3713,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3640,10 +3746,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697667</v>
+        <v>697710</v>
       </c>
       <c r="R28" t="n">
-        <v>6556761</v>
+        <v>6556732</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,7 +3781,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3685,7 +3791,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3712,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540883</v>
+        <v>122540888</v>
       </c>
       <c r="B29" t="n">
-        <v>4776</v>
+        <v>100490</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3728,34 +3839,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102306</v>
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697616</v>
+        <v>697678</v>
       </c>
       <c r="R29" t="n">
-        <v>6556904</v>
+        <v>6556802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,7 +3898,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3797,7 +3908,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3808,21 +3919,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3839,10 +3935,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540889</v>
+        <v>122540887</v>
       </c>
       <c r="B30" t="n">
-        <v>110349</v>
+        <v>110362</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,6 +3953,11 @@
       <c r="E30" t="n">
         <v>219711</v>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Sanicula europaea</t>
@@ -3874,10 +3975,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697668</v>
+        <v>697678</v>
       </c>
       <c r="R30" t="n">
-        <v>6556773</v>
+        <v>6556802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3909,7 +4010,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,7 +4020,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,10 +4047,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540888</v>
+        <v>122540897</v>
       </c>
       <c r="B31" t="n">
-        <v>100477</v>
+        <v>94842</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3962,29 +4063,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>210</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697678</v>
+        <v>697581</v>
       </c>
       <c r="R31" t="n">
-        <v>6556802</v>
+        <v>6556970</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4016,7 +4131,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4141,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4037,6 +4152,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4071,6 +4206,11 @@
       <c r="E32" t="n">
         <v>106554</v>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Scolytus ratzeburgii</t>
@@ -4149,6 +4289,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
@@ -4180,10 +4325,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540890</v>
+        <v>122540891</v>
       </c>
       <c r="B33" t="n">
-        <v>110349</v>
+        <v>98224</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4192,23 +4337,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219711</v>
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -4287,10 +4446,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540896</v>
+        <v>122540881</v>
       </c>
       <c r="B34" t="n">
-        <v>110349</v>
+        <v>94746</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4303,16 +4462,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219711</v>
+        <v>2818</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4322,13 +4486,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697607</v>
+        <v>697597</v>
       </c>
       <c r="R34" t="n">
-        <v>6556976</v>
+        <v>6556987</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4357,7 +4521,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4367,7 +4531,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,6 +4542,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4394,10 +4578,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540886</v>
+        <v>122540893</v>
       </c>
       <c r="B35" t="n">
-        <v>98233</v>
+        <v>100490</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,34 +4594,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219862</v>
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697681</v>
+        <v>697710</v>
       </c>
       <c r="R35" t="n">
-        <v>6556807</v>
+        <v>6556732</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4469,7 +4653,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4479,7 +4663,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4506,10 +4690,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540884</v>
+        <v>122540890</v>
       </c>
       <c r="B36" t="n">
-        <v>8441</v>
+        <v>110362</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4522,34 +4706,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>219711</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697609</v>
+        <v>697667</v>
       </c>
       <c r="R36" t="n">
-        <v>6556889</v>
+        <v>6556761</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4581,7 +4765,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4591,7 +4775,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,16 +4786,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4628,10 +4802,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540887</v>
+        <v>122540896</v>
       </c>
       <c r="B37" t="n">
-        <v>110349</v>
+        <v>110362</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4646,6 +4820,11 @@
       <c r="E37" t="n">
         <v>219711</v>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Sanicula europaea</t>
@@ -4663,10 +4842,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697678</v>
+        <v>697607</v>
       </c>
       <c r="R37" t="n">
-        <v>6556802</v>
+        <v>6556976</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4698,7 +4877,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,7 +4887,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4735,10 +4914,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122540897</v>
+        <v>122540889</v>
       </c>
       <c r="B38" t="n">
-        <v>94829</v>
+        <v>110362</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4751,38 +4930,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>210</v>
+        <v>219711</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697581</v>
+        <v>697668</v>
       </c>
       <c r="R38" t="n">
-        <v>6556970</v>
+        <v>6556773</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4814,7 +4989,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4824,7 +4999,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,21 +5010,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4866,10 +5026,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540881</v>
+        <v>122540886</v>
       </c>
       <c r="B39" t="n">
-        <v>94733</v>
+        <v>98246</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4882,32 +5042,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>219862</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697597</v>
+        <v>697681</v>
       </c>
       <c r="R39" t="n">
-        <v>6556987</v>
+        <v>6556807</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4936,7 +5106,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4946,7 +5116,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4957,21 +5127,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4988,14 +5143,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122540885</v>
+        <v>122540898</v>
       </c>
       <c r="B40" t="n">
-        <v>94876</v>
+        <v>94842</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5004,29 +5159,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2170</v>
+        <v>210</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697628</v>
+        <v>697586</v>
       </c>
       <c r="R40" t="n">
-        <v>6556873</v>
+        <v>6556969</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5058,7 +5227,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5068,7 +5237,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5079,6 +5248,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5095,14 +5284,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122540898</v>
+        <v>122540885</v>
       </c>
       <c r="B41" t="n">
-        <v>94829</v>
+        <v>94889</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5111,38 +5300,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>210</v>
+        <v>2170</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>697586</v>
+        <v>697628</v>
       </c>
       <c r="R41" t="n">
-        <v>6556969</v>
+        <v>6556873</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5174,7 +5359,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5184,7 +5369,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5195,21 +5380,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5219,10 +5389,147 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
+          <t>Birgitta Tulin, Åsa Back, Klas Magnusson, Karin Engshagen, Kalle Skarin, Per Flodby, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122540882</v>
+      </c>
+      <c r="B42" t="n">
+        <v>96302</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>232</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedsäckmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Calypogeia suecica</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>697597</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6556987</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
           <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122311404</v>
+        <v>122310585</v>
       </c>
       <c r="B14" t="n">
-        <v>110362</v>
+        <v>90859</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,45 +2064,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697695</v>
+        <v>697618</v>
       </c>
       <c r="R14" t="n">
-        <v>6556744</v>
+        <v>6556920</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122310983</v>
+        <v>122311010</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>110375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,35 +2183,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2216,13 +2215,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697700</v>
+        <v>697679</v>
       </c>
       <c r="R15" t="n">
-        <v>6556781</v>
+        <v>6556777</v>
       </c>
       <c r="S15" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122310585</v>
+        <v>122309800</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,25 +2299,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2328,6 +2327,8 @@
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2335,13 +2336,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697618</v>
+        <v>697596</v>
       </c>
       <c r="R16" t="n">
-        <v>6556920</v>
+        <v>6557005</v>
       </c>
       <c r="S16" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2370,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122309800</v>
+        <v>122311404</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>110375</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,46 +2424,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697596</v>
+        <v>697695</v>
       </c>
       <c r="R17" t="n">
-        <v>6557005</v>
+        <v>6556744</v>
       </c>
       <c r="S17" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2487,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2497,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2528,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122311010</v>
+        <v>122310912</v>
       </c>
       <c r="B18" t="n">
-        <v>110362</v>
+        <v>100503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,21 +2540,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2572,13 +2568,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697679</v>
+        <v>697686</v>
       </c>
       <c r="R18" t="n">
-        <v>6556777</v>
+        <v>6556802</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2607,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,10 +2640,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122310912</v>
+        <v>122310983</v>
       </c>
       <c r="B19" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2656,31 +2652,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697686</v>
+        <v>697700</v>
       </c>
       <c r="R19" t="n">
-        <v>6556802</v>
+        <v>6556781</v>
       </c>
       <c r="S19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122323928</v>
+        <v>122323737</v>
       </c>
       <c r="B20" t="n">
-        <v>110362</v>
+        <v>110375</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697678</v>
+        <v>697676</v>
       </c>
       <c r="R20" t="n">
-        <v>6556740</v>
+        <v>6556742</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122323737</v>
+        <v>122323126</v>
       </c>
       <c r="B21" t="n">
-        <v>110362</v>
+        <v>110375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697676</v>
+        <v>697732</v>
       </c>
       <c r="R21" t="n">
-        <v>6556742</v>
+        <v>6556749</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122323126</v>
+        <v>122323326</v>
       </c>
       <c r="B22" t="n">
-        <v>110362</v>
+        <v>110375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697732</v>
+        <v>697701</v>
       </c>
       <c r="R22" t="n">
-        <v>6556749</v>
+        <v>6556732</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122324705</v>
+        <v>122324459</v>
       </c>
       <c r="B23" t="n">
-        <v>90846</v>
+        <v>95009</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3108,25 +3108,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697615</v>
+        <v>697641</v>
       </c>
       <c r="R23" t="n">
-        <v>6556966</v>
+        <v>6556847</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122324459</v>
+        <v>122324705</v>
       </c>
       <c r="B24" t="n">
-        <v>94996</v>
+        <v>90859</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3220,25 +3220,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3248,13 +3248,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697641</v>
+        <v>697615</v>
       </c>
       <c r="R24" t="n">
-        <v>6556847</v>
+        <v>6556966</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122323326</v>
+        <v>122323928</v>
       </c>
       <c r="B25" t="n">
-        <v>110362</v>
+        <v>110375</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697701</v>
+        <v>697678</v>
       </c>
       <c r="R25" t="n">
-        <v>6556732</v>
+        <v>6556740</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540883</v>
+        <v>122540888</v>
       </c>
       <c r="B26" t="n">
-        <v>4776</v>
+        <v>100503</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,39 +3448,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697616</v>
+        <v>697678</v>
       </c>
       <c r="R26" t="n">
-        <v>6556904</v>
+        <v>6556802</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3512,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3522,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,26 +3528,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3569,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540884</v>
+        <v>122540896</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>110375</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3585,39 +3560,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697609</v>
+        <v>697607</v>
       </c>
       <c r="R27" t="n">
-        <v>6556889</v>
+        <v>6556976</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3649,7 +3619,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,7 +3629,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3670,21 +3640,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3701,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540895</v>
+        <v>122540889</v>
       </c>
       <c r="B28" t="n">
-        <v>57399</v>
+        <v>110375</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3713,43 +3668,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697710</v>
+        <v>697668</v>
       </c>
       <c r="R28" t="n">
-        <v>6556732</v>
+        <v>6556773</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3781,7 +3731,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3791,12 +3741,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3823,10 +3768,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540888</v>
+        <v>122540897</v>
       </c>
       <c r="B29" t="n">
-        <v>100490</v>
+        <v>94855</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3839,34 +3784,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697678</v>
+        <v>697581</v>
       </c>
       <c r="R29" t="n">
-        <v>6556802</v>
+        <v>6556970</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3898,7 +3852,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3908,7 +3862,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,6 +3873,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3935,10 +3909,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540887</v>
+        <v>122540883</v>
       </c>
       <c r="B30" t="n">
-        <v>110362</v>
+        <v>4776</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3951,34 +3925,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219711</v>
+        <v>102306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697678</v>
+        <v>697616</v>
       </c>
       <c r="R30" t="n">
-        <v>6556802</v>
+        <v>6556904</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,7 +3989,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4020,7 +3999,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4031,6 +4010,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4047,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540897</v>
+        <v>122540893</v>
       </c>
       <c r="B31" t="n">
-        <v>94842</v>
+        <v>100503</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4063,43 +4062,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697581</v>
+        <v>697710</v>
       </c>
       <c r="R31" t="n">
-        <v>6556970</v>
+        <v>6556732</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4131,7 +4121,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4141,7 +4131,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4152,26 +4142,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4188,10 +4158,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540878</v>
+        <v>122540886</v>
       </c>
       <c r="B32" t="n">
-        <v>8430</v>
+        <v>98259</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4204,27 +4174,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>219862</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4233,10 +4203,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697600</v>
+        <v>697681</v>
       </c>
       <c r="R32" t="n">
-        <v>6557016</v>
+        <v>6556807</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4268,7 +4238,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4278,7 +4248,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4289,26 +4259,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Betula # Barklös björklåga.</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4328,7 +4278,7 @@
         <v>122540891</v>
       </c>
       <c r="B33" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4446,10 +4396,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540881</v>
+        <v>122540884</v>
       </c>
       <c r="B34" t="n">
-        <v>94746</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4462,37 +4412,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2818</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697597</v>
+        <v>697609</v>
       </c>
       <c r="R34" t="n">
-        <v>6556987</v>
+        <v>6556889</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4521,7 +4476,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4531,7 +4486,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4545,22 +4500,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4578,10 +4528,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540893</v>
+        <v>122540881</v>
       </c>
       <c r="B35" t="n">
-        <v>100490</v>
+        <v>94759</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4594,21 +4544,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4618,13 +4568,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697710</v>
+        <v>697597</v>
       </c>
       <c r="R35" t="n">
-        <v>6556732</v>
+        <v>6556987</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4653,7 +4603,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4663,7 +4613,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4674,6 +4624,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4690,10 +4660,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540890</v>
+        <v>122540878</v>
       </c>
       <c r="B36" t="n">
-        <v>110362</v>
+        <v>8430</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4706,34 +4676,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697667</v>
+        <v>697600</v>
       </c>
       <c r="R36" t="n">
-        <v>6556761</v>
+        <v>6557016</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4765,7 +4740,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4775,7 +4750,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4786,6 +4761,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4802,10 +4797,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540896</v>
+        <v>122540895</v>
       </c>
       <c r="B37" t="n">
-        <v>110362</v>
+        <v>57399</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4814,38 +4809,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697607</v>
+        <v>697710</v>
       </c>
       <c r="R37" t="n">
-        <v>6556976</v>
+        <v>6556732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4887,7 +4887,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4914,10 +4919,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122540889</v>
+        <v>122540887</v>
       </c>
       <c r="B38" t="n">
-        <v>110362</v>
+        <v>110375</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697668</v>
+        <v>697678</v>
       </c>
       <c r="R38" t="n">
-        <v>6556773</v>
+        <v>6556802</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4989,7 +4994,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4999,7 +5004,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5026,10 +5031,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540886</v>
+        <v>122540890</v>
       </c>
       <c r="B39" t="n">
-        <v>98246</v>
+        <v>110375</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5042,39 +5047,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697681</v>
+        <v>697667</v>
       </c>
       <c r="R39" t="n">
-        <v>6556807</v>
+        <v>6556761</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5143,10 +5143,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122540898</v>
+        <v>122540885</v>
       </c>
       <c r="B40" t="n">
-        <v>94842</v>
+        <v>94902</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5159,43 +5159,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>210</v>
+        <v>2170</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697586</v>
+        <v>697628</v>
       </c>
       <c r="R40" t="n">
-        <v>6556969</v>
+        <v>6556873</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5227,7 +5218,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5237,7 +5228,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5248,26 +5239,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5284,10 +5255,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122540885</v>
+        <v>122540898</v>
       </c>
       <c r="B41" t="n">
-        <v>94889</v>
+        <v>94855</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5300,34 +5271,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2170</v>
+        <v>210</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>697628</v>
+        <v>697586</v>
       </c>
       <c r="R41" t="n">
-        <v>6556873</v>
+        <v>6556969</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5359,7 +5339,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5369,7 +5349,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5380,6 +5360,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Birgitta Tulin, Åsa Back, Klas Magnusson, Karin Engshagen, Kalle Skarin, Per Flodby, Emilia Blixt</t>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -4528,10 +4528,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540881</v>
+        <v>122540878</v>
       </c>
       <c r="B35" t="n">
-        <v>94759</v>
+        <v>8430</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4544,37 +4544,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697597</v>
+        <v>697600</v>
       </c>
       <c r="R35" t="n">
-        <v>6556987</v>
+        <v>6557016</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4603,7 +4608,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4613,7 +4618,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4627,22 +4632,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
+          <t>Barklös björklåga.</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+          <t>Betula # Barklös björklåga.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4660,10 +4665,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540878</v>
+        <v>122540881</v>
       </c>
       <c r="B36" t="n">
-        <v>8430</v>
+        <v>94759</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4676,42 +4681,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697600</v>
+        <v>697597</v>
       </c>
       <c r="R36" t="n">
-        <v>6557016</v>
+        <v>6556987</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Barklös björklåga.</t>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Betula # Barklös björklåga.</t>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122310585</v>
+        <v>122309800</v>
       </c>
       <c r="B14" t="n">
-        <v>90859</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,25 +2064,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2092,6 +2092,8 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2099,13 +2101,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697618</v>
+        <v>697596</v>
       </c>
       <c r="R14" t="n">
-        <v>6556920</v>
+        <v>6557005</v>
       </c>
       <c r="S14" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122311010</v>
+        <v>122310912</v>
       </c>
       <c r="B15" t="n">
-        <v>110375</v>
+        <v>100503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,21 +2189,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2215,13 +2217,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697679</v>
+        <v>697686</v>
       </c>
       <c r="R15" t="n">
-        <v>6556777</v>
+        <v>6556802</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2250,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122309800</v>
+        <v>122311404</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>110375</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,46 +2305,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697596</v>
+        <v>697695</v>
       </c>
       <c r="R16" t="n">
-        <v>6557005</v>
+        <v>6556744</v>
       </c>
       <c r="S16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2371,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,7 +2405,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122311404</v>
+        <v>122311010</v>
       </c>
       <c r="B17" t="n">
         <v>110375</v>
@@ -2448,14 +2445,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697695</v>
+        <v>697679</v>
       </c>
       <c r="R17" t="n">
-        <v>6556744</v>
+        <v>6556777</v>
       </c>
       <c r="S17" t="n">
         <v>11</v>
@@ -2487,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2497,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,10 +2521,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122310912</v>
+        <v>122310585</v>
       </c>
       <c r="B18" t="n">
-        <v>100503</v>
+        <v>90859</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,31 +2533,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697686</v>
+        <v>697618</v>
       </c>
       <c r="R18" t="n">
-        <v>6556802</v>
+        <v>6556920</v>
       </c>
       <c r="S18" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2760,7 +2760,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122323737</v>
+        <v>122323126</v>
       </c>
       <c r="B20" t="n">
         <v>110375</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697676</v>
+        <v>697732</v>
       </c>
       <c r="R20" t="n">
-        <v>6556742</v>
+        <v>6556749</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,7 +2872,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122323126</v>
+        <v>122323326</v>
       </c>
       <c r="B21" t="n">
         <v>110375</v>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697732</v>
+        <v>697701</v>
       </c>
       <c r="R21" t="n">
-        <v>6556749</v>
+        <v>6556732</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122323326</v>
+        <v>122324459</v>
       </c>
       <c r="B22" t="n">
-        <v>110375</v>
+        <v>95009</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,34 +3000,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697701</v>
+        <v>697641</v>
       </c>
       <c r="R22" t="n">
-        <v>6556732</v>
+        <v>6556847</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122324459</v>
+        <v>122323928</v>
       </c>
       <c r="B23" t="n">
-        <v>95009</v>
+        <v>110375</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,34 +3112,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697641</v>
+        <v>697678</v>
       </c>
       <c r="R23" t="n">
-        <v>6556847</v>
+        <v>6556740</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122324705</v>
+        <v>122323737</v>
       </c>
       <c r="B24" t="n">
-        <v>90859</v>
+        <v>110375</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3220,41 +3220,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697615</v>
+        <v>697676</v>
       </c>
       <c r="R24" t="n">
-        <v>6556966</v>
+        <v>6556742</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122323928</v>
+        <v>122324705</v>
       </c>
       <c r="B25" t="n">
-        <v>110375</v>
+        <v>90859</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,41 +3332,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697678</v>
+        <v>697615</v>
       </c>
       <c r="R25" t="n">
-        <v>6556740</v>
+        <v>6556966</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540888</v>
+        <v>122540889</v>
       </c>
       <c r="B26" t="n">
-        <v>100503</v>
+        <v>110375</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697678</v>
+        <v>697668</v>
       </c>
       <c r="R26" t="n">
-        <v>6556802</v>
+        <v>6556773</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540896</v>
+        <v>122540891</v>
       </c>
       <c r="B27" t="n">
-        <v>110375</v>
+        <v>98237</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,38 +3556,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697607</v>
+        <v>697667</v>
       </c>
       <c r="R27" t="n">
-        <v>6556976</v>
+        <v>6556761</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3619,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3629,7 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540889</v>
+        <v>122540883</v>
       </c>
       <c r="B28" t="n">
-        <v>110375</v>
+        <v>4776</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3672,34 +3681,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697668</v>
+        <v>697616</v>
       </c>
       <c r="R28" t="n">
-        <v>6556773</v>
+        <v>6556904</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3731,7 +3745,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3755,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3752,6 +3766,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3768,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540897</v>
+        <v>122540884</v>
       </c>
       <c r="B29" t="n">
-        <v>94855</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3784,31 +3818,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>210</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3817,10 +3847,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697581</v>
+        <v>697609</v>
       </c>
       <c r="R29" t="n">
-        <v>6556970</v>
+        <v>6556889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3852,7 +3882,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3862,7 +3892,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,14 +3914,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3909,10 +3934,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540883</v>
+        <v>122540896</v>
       </c>
       <c r="B30" t="n">
-        <v>4776</v>
+        <v>110375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3925,39 +3950,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>219711</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697616</v>
+        <v>697607</v>
       </c>
       <c r="R30" t="n">
-        <v>6556904</v>
+        <v>6556976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3989,7 +4009,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3999,7 +4019,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,26 +4030,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540893</v>
+        <v>122540878</v>
       </c>
       <c r="B31" t="n">
-        <v>100503</v>
+        <v>8430</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4062,34 +4062,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697710</v>
+        <v>697600</v>
       </c>
       <c r="R31" t="n">
-        <v>6556732</v>
+        <v>6557016</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4121,7 +4126,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4131,7 +4136,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4142,6 +4147,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4158,10 +4183,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540886</v>
+        <v>122540881</v>
       </c>
       <c r="B32" t="n">
-        <v>98259</v>
+        <v>94759</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4174,42 +4199,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219862</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697681</v>
+        <v>697597</v>
       </c>
       <c r="R32" t="n">
-        <v>6556807</v>
+        <v>6556987</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4238,7 +4258,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4248,7 +4268,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4259,6 +4279,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4275,10 +4315,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540891</v>
+        <v>122540895</v>
       </c>
       <c r="B33" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4287,35 +4327,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4324,10 +4360,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697667</v>
+        <v>697710</v>
       </c>
       <c r="R33" t="n">
-        <v>6556761</v>
+        <v>6556732</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4359,7 +4395,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4369,7 +4405,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4396,10 +4437,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540884</v>
+        <v>122540888</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>100503</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4412,39 +4453,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697609</v>
+        <v>697678</v>
       </c>
       <c r="R34" t="n">
-        <v>6556889</v>
+        <v>6556802</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4476,7 +4512,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4486,7 +4522,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4497,21 +4533,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4528,10 +4549,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540878</v>
+        <v>122540887</v>
       </c>
       <c r="B35" t="n">
-        <v>8430</v>
+        <v>110375</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4544,39 +4565,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697600</v>
+        <v>697678</v>
       </c>
       <c r="R35" t="n">
-        <v>6557016</v>
+        <v>6556802</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4608,7 +4624,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4618,7 +4634,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,26 +4645,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Betula # Barklös björklåga.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4665,10 +4661,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540881</v>
+        <v>122540890</v>
       </c>
       <c r="B36" t="n">
-        <v>94759</v>
+        <v>110375</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4681,21 +4677,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2818</v>
+        <v>219711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4705,13 +4701,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697597</v>
+        <v>697667</v>
       </c>
       <c r="R36" t="n">
-        <v>6556987</v>
+        <v>6556761</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4740,7 +4736,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4750,7 +4746,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4761,26 +4757,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4797,10 +4773,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540895</v>
+        <v>122540893</v>
       </c>
       <c r="B37" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4809,33 +4785,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -4877,7 +4848,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4887,12 +4858,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4919,10 +4885,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122540887</v>
+        <v>122540897</v>
       </c>
       <c r="B38" t="n">
-        <v>110375</v>
+        <v>94855</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4935,34 +4901,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219711</v>
+        <v>210</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697678</v>
+        <v>697581</v>
       </c>
       <c r="R38" t="n">
-        <v>6556802</v>
+        <v>6556970</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4994,7 +4969,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5004,7 +4979,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5015,6 +4990,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5031,10 +5026,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540890</v>
+        <v>122540886</v>
       </c>
       <c r="B39" t="n">
-        <v>110375</v>
+        <v>98259</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5047,34 +5042,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697667</v>
+        <v>697681</v>
       </c>
       <c r="R39" t="n">
-        <v>6556761</v>
+        <v>6556807</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2872,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122323326</v>
+        <v>122324459</v>
       </c>
       <c r="B21" t="n">
-        <v>110375</v>
+        <v>95009</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2888,34 +2888,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697701</v>
+        <v>697641</v>
       </c>
       <c r="R21" t="n">
-        <v>6556732</v>
+        <v>6556847</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122324459</v>
+        <v>122323326</v>
       </c>
       <c r="B22" t="n">
-        <v>95009</v>
+        <v>110375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,34 +3000,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697641</v>
+        <v>697701</v>
       </c>
       <c r="R22" t="n">
-        <v>6556847</v>
+        <v>6556732</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3802,10 +3802,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540884</v>
+        <v>122540896</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>110375</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3818,39 +3818,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697609</v>
+        <v>697607</v>
       </c>
       <c r="R29" t="n">
-        <v>6556889</v>
+        <v>6556976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3882,7 +3877,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3892,7 +3887,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,21 +3898,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3934,10 +3914,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540896</v>
+        <v>122540884</v>
       </c>
       <c r="B30" t="n">
-        <v>110375</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3950,34 +3930,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697607</v>
+        <v>697609</v>
       </c>
       <c r="R30" t="n">
-        <v>6556976</v>
+        <v>6556889</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4009,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4019,7 +4004,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4030,6 +4015,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4183,10 +4183,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540881</v>
+        <v>122540895</v>
       </c>
       <c r="B32" t="n">
-        <v>94759</v>
+        <v>57399</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4195,41 +4195,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697597</v>
+        <v>697710</v>
       </c>
       <c r="R32" t="n">
-        <v>6556987</v>
+        <v>6556732</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4258,7 +4263,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4268,7 +4273,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4279,26 +4289,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4315,10 +4305,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540895</v>
+        <v>122540881</v>
       </c>
       <c r="B33" t="n">
-        <v>57399</v>
+        <v>94759</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4327,46 +4317,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697710</v>
+        <v>697597</v>
       </c>
       <c r="R33" t="n">
-        <v>6556732</v>
+        <v>6556987</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4395,7 +4380,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4405,12 +4390,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4421,6 +4401,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122309800</v>
+        <v>122311010</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>110378</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,32 +2068,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2101,13 +2096,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697596</v>
+        <v>697679</v>
       </c>
       <c r="R14" t="n">
-        <v>6557005</v>
+        <v>6556777</v>
       </c>
       <c r="S14" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2136,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,7 +2171,7 @@
         <v>122310912</v>
       </c>
       <c r="B15" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2289,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122311404</v>
+        <v>122310983</v>
       </c>
       <c r="B16" t="n">
-        <v>110375</v>
+        <v>57399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,45 +2296,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697695</v>
+        <v>697700</v>
       </c>
       <c r="R16" t="n">
-        <v>6556744</v>
+        <v>6556781</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2368,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122311010</v>
+        <v>122310585</v>
       </c>
       <c r="B17" t="n">
-        <v>110375</v>
+        <v>90853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,31 +2416,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2449,13 +2451,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697679</v>
+        <v>697618</v>
       </c>
       <c r="R17" t="n">
-        <v>6556777</v>
+        <v>6556920</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2484,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122310585</v>
+        <v>122309800</v>
       </c>
       <c r="B18" t="n">
-        <v>90859</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,25 +2535,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2561,6 +2563,8 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2568,13 +2572,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697618</v>
+        <v>697596</v>
       </c>
       <c r="R18" t="n">
-        <v>6556920</v>
+        <v>6557005</v>
       </c>
       <c r="S18" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122310983</v>
+        <v>122311404</v>
       </c>
       <c r="B19" t="n">
-        <v>57399</v>
+        <v>110378</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,49 +2656,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697700</v>
+        <v>697695</v>
       </c>
       <c r="R19" t="n">
-        <v>6556781</v>
+        <v>6556744</v>
       </c>
       <c r="S19" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122323126</v>
+        <v>122323326</v>
       </c>
       <c r="B20" t="n">
-        <v>110375</v>
+        <v>110378</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697732</v>
+        <v>697701</v>
       </c>
       <c r="R20" t="n">
-        <v>6556749</v>
+        <v>6556732</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122324459</v>
+        <v>122324705</v>
       </c>
       <c r="B21" t="n">
-        <v>95009</v>
+        <v>90853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,25 +2884,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2912,13 +2912,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697641</v>
+        <v>697615</v>
       </c>
       <c r="R21" t="n">
-        <v>6556847</v>
+        <v>6556966</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122323326</v>
+        <v>122323928</v>
       </c>
       <c r="B22" t="n">
-        <v>110375</v>
+        <v>110378</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697701</v>
+        <v>697678</v>
       </c>
       <c r="R22" t="n">
-        <v>6556732</v>
+        <v>6556740</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122323928</v>
+        <v>122323126</v>
       </c>
       <c r="B23" t="n">
-        <v>110375</v>
+        <v>110378</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697678</v>
+        <v>697732</v>
       </c>
       <c r="R23" t="n">
-        <v>6556740</v>
+        <v>6556749</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122323737</v>
+        <v>122324459</v>
       </c>
       <c r="B24" t="n">
-        <v>110375</v>
+        <v>95011</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,34 +3224,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697676</v>
+        <v>697641</v>
       </c>
       <c r="R24" t="n">
-        <v>6556742</v>
+        <v>6556847</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122324705</v>
+        <v>122323737</v>
       </c>
       <c r="B25" t="n">
-        <v>90859</v>
+        <v>110378</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,41 +3332,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697615</v>
+        <v>697676</v>
       </c>
       <c r="R25" t="n">
-        <v>6556966</v>
+        <v>6556742</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540889</v>
+        <v>122540883</v>
       </c>
       <c r="B26" t="n">
-        <v>110375</v>
+        <v>4776</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,34 +3448,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>102306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697668</v>
+        <v>697616</v>
       </c>
       <c r="R26" t="n">
-        <v>6556773</v>
+        <v>6556904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,6 +3533,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3544,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540891</v>
+        <v>122540895</v>
       </c>
       <c r="B27" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,35 +3581,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3593,10 +3614,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697667</v>
+        <v>697710</v>
       </c>
       <c r="R27" t="n">
-        <v>6556761</v>
+        <v>6556732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3628,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3659,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,10 +3691,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540883</v>
+        <v>122540897</v>
       </c>
       <c r="B28" t="n">
-        <v>4776</v>
+        <v>94857</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3681,27 +3707,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>210</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3710,10 +3740,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697616</v>
+        <v>697581</v>
       </c>
       <c r="R28" t="n">
-        <v>6556904</v>
+        <v>6556970</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3745,7 +3775,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3755,7 +3785,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3769,22 +3799,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Tallågor i stockbro över skogsbäck.</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3802,10 +3832,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540896</v>
+        <v>122540878</v>
       </c>
       <c r="B29" t="n">
-        <v>110375</v>
+        <v>8430</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3818,34 +3848,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697607</v>
+        <v>697600</v>
       </c>
       <c r="R29" t="n">
-        <v>6556976</v>
+        <v>6557016</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3877,7 +3912,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3887,7 +3922,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3898,6 +3933,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4046,10 +4101,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540878</v>
+        <v>122540887</v>
       </c>
       <c r="B31" t="n">
-        <v>8430</v>
+        <v>110378</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4062,39 +4117,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>219711</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697600</v>
+        <v>697678</v>
       </c>
       <c r="R31" t="n">
-        <v>6557016</v>
+        <v>6556802</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4126,7 +4176,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4136,7 +4186,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4147,26 +4197,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Betula # Barklös björklåga.</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4183,10 +4213,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540895</v>
+        <v>122540896</v>
       </c>
       <c r="B32" t="n">
-        <v>57399</v>
+        <v>110378</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4195,43 +4225,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697710</v>
+        <v>697607</v>
       </c>
       <c r="R32" t="n">
-        <v>6556732</v>
+        <v>6556976</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4263,7 +4288,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4273,12 +4298,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4305,10 +4325,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540881</v>
+        <v>122540889</v>
       </c>
       <c r="B33" t="n">
-        <v>94759</v>
+        <v>110378</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4321,21 +4341,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>219711</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4345,13 +4365,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697597</v>
+        <v>697668</v>
       </c>
       <c r="R33" t="n">
-        <v>6556987</v>
+        <v>6556773</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4380,7 +4400,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4390,7 +4410,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4401,26 +4421,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4437,10 +4437,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540888</v>
+        <v>122540886</v>
       </c>
       <c r="B34" t="n">
-        <v>100503</v>
+        <v>98262</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4453,34 +4453,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697678</v>
+        <v>697681</v>
       </c>
       <c r="R34" t="n">
-        <v>6556802</v>
+        <v>6556807</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4512,7 +4517,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4522,7 +4527,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4549,10 +4554,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540887</v>
+        <v>122540881</v>
       </c>
       <c r="B35" t="n">
-        <v>110375</v>
+        <v>94761</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4565,21 +4570,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>2818</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4589,13 +4594,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697678</v>
+        <v>697597</v>
       </c>
       <c r="R35" t="n">
-        <v>6556802</v>
+        <v>6556987</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4624,7 +4629,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4634,7 +4639,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4645,6 +4650,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4664,7 +4689,7 @@
         <v>122540890</v>
       </c>
       <c r="B36" t="n">
-        <v>110375</v>
+        <v>110378</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4773,10 +4798,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540893</v>
+        <v>122540891</v>
       </c>
       <c r="B37" t="n">
-        <v>100503</v>
+        <v>98240</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4785,38 +4810,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697710</v>
+        <v>697667</v>
       </c>
       <c r="R37" t="n">
-        <v>6556732</v>
+        <v>6556761</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4848,7 +4882,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4858,7 +4892,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4885,10 +4919,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122540897</v>
+        <v>122540888</v>
       </c>
       <c r="B38" t="n">
-        <v>94855</v>
+        <v>100506</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4901,43 +4935,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697581</v>
+        <v>697678</v>
       </c>
       <c r="R38" t="n">
-        <v>6556970</v>
+        <v>6556802</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4969,7 +4994,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4979,7 +5004,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4990,26 +5015,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5026,10 +5031,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540886</v>
+        <v>122540893</v>
       </c>
       <c r="B39" t="n">
-        <v>98259</v>
+        <v>100506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5042,39 +5047,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697681</v>
+        <v>697710</v>
       </c>
       <c r="R39" t="n">
-        <v>6556807</v>
+        <v>6556732</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5143,10 +5143,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122540885</v>
+        <v>122540898</v>
       </c>
       <c r="B40" t="n">
-        <v>94902</v>
+        <v>94857</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5159,34 +5159,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2170</v>
+        <v>210</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697628</v>
+        <v>697586</v>
       </c>
       <c r="R40" t="n">
-        <v>6556873</v>
+        <v>6556969</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5218,7 +5227,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5228,7 +5237,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5239,6 +5248,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5255,10 +5284,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122540898</v>
+        <v>122540885</v>
       </c>
       <c r="B41" t="n">
-        <v>94855</v>
+        <v>94904</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5271,43 +5300,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>210</v>
+        <v>2170</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>697586</v>
+        <v>697628</v>
       </c>
       <c r="R41" t="n">
-        <v>6556969</v>
+        <v>6556873</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5339,7 +5359,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5349,7 +5369,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5360,26 +5380,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5399,7 +5399,7 @@
         <v>122540882</v>
       </c>
       <c r="B42" t="n">
-        <v>96302</v>
+        <v>96305</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122311010</v>
+        <v>122310585</v>
       </c>
       <c r="B14" t="n">
-        <v>110378</v>
+        <v>90853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,31 +2064,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2096,13 +2099,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697679</v>
+        <v>697618</v>
       </c>
       <c r="R14" t="n">
-        <v>6556777</v>
+        <v>6556920</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122310912</v>
+        <v>122311010</v>
       </c>
       <c r="B15" t="n">
-        <v>100506</v>
+        <v>110378</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,21 +2187,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2212,13 +2215,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697686</v>
+        <v>697679</v>
       </c>
       <c r="R15" t="n">
-        <v>6556802</v>
+        <v>6556777</v>
       </c>
       <c r="S15" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2247,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2404,10 +2407,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122310585</v>
+        <v>122309800</v>
       </c>
       <c r="B17" t="n">
-        <v>90853</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,25 +2419,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2444,6 +2447,8 @@
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2451,13 +2456,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697618</v>
+        <v>697596</v>
       </c>
       <c r="R17" t="n">
-        <v>6556920</v>
+        <v>6557005</v>
       </c>
       <c r="S17" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2528,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122309800</v>
+        <v>122310912</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>100506</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,32 +2544,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697596</v>
+        <v>697686</v>
       </c>
       <c r="R18" t="n">
-        <v>6557005</v>
+        <v>6556802</v>
       </c>
       <c r="S18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2760,7 +2760,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122323326</v>
+        <v>122323737</v>
       </c>
       <c r="B20" t="n">
         <v>110378</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697701</v>
+        <v>697676</v>
       </c>
       <c r="R20" t="n">
-        <v>6556732</v>
+        <v>6556742</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122324705</v>
+        <v>122323126</v>
       </c>
       <c r="B21" t="n">
-        <v>90853</v>
+        <v>110378</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,41 +2884,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697615</v>
+        <v>697732</v>
       </c>
       <c r="R21" t="n">
-        <v>6556966</v>
+        <v>6556749</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122323928</v>
+        <v>122324459</v>
       </c>
       <c r="B22" t="n">
-        <v>110378</v>
+        <v>95011</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,34 +3000,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697678</v>
+        <v>697641</v>
       </c>
       <c r="R22" t="n">
-        <v>6556740</v>
+        <v>6556847</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122323126</v>
+        <v>122323326</v>
       </c>
       <c r="B23" t="n">
         <v>110378</v>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697732</v>
+        <v>697701</v>
       </c>
       <c r="R23" t="n">
-        <v>6556749</v>
+        <v>6556732</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122324459</v>
+        <v>122324705</v>
       </c>
       <c r="B24" t="n">
-        <v>95011</v>
+        <v>90853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3220,25 +3220,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3248,13 +3248,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697641</v>
+        <v>697615</v>
       </c>
       <c r="R24" t="n">
-        <v>6556847</v>
+        <v>6556966</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122323737</v>
+        <v>122323928</v>
       </c>
       <c r="B25" t="n">
         <v>110378</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697676</v>
+        <v>697678</v>
       </c>
       <c r="R25" t="n">
-        <v>6556742</v>
+        <v>6556740</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540883</v>
+        <v>122540889</v>
       </c>
       <c r="B26" t="n">
-        <v>4776</v>
+        <v>110378</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,39 +3448,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697616</v>
+        <v>697668</v>
       </c>
       <c r="R26" t="n">
-        <v>6556904</v>
+        <v>6556773</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3512,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3522,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,26 +3528,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3569,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540895</v>
+        <v>122540891</v>
       </c>
       <c r="B27" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,31 +3556,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3614,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697710</v>
+        <v>697667</v>
       </c>
       <c r="R27" t="n">
-        <v>6556732</v>
+        <v>6556761</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3649,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,12 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3691,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540897</v>
+        <v>122540893</v>
       </c>
       <c r="B28" t="n">
-        <v>94857</v>
+        <v>100506</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3707,43 +3681,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697581</v>
+        <v>697710</v>
       </c>
       <c r="R28" t="n">
-        <v>6556970</v>
+        <v>6556732</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3775,7 +3740,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3785,7 +3750,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3796,26 +3761,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3832,10 +3777,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540878</v>
+        <v>122540890</v>
       </c>
       <c r="B29" t="n">
-        <v>8430</v>
+        <v>110378</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3848,39 +3793,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>219711</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697600</v>
+        <v>697667</v>
       </c>
       <c r="R29" t="n">
-        <v>6557016</v>
+        <v>6556761</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3912,7 +3852,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3922,7 +3862,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3933,26 +3873,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Betula # Barklös björklåga.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3969,10 +3889,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540884</v>
+        <v>122540886</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>98262</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3985,27 +3905,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>219862</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4014,10 +3934,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697609</v>
+        <v>697681</v>
       </c>
       <c r="R30" t="n">
-        <v>6556889</v>
+        <v>6556807</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4049,7 +3969,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4059,7 +3979,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4070,21 +3990,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4101,10 +4006,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540887</v>
+        <v>122540883</v>
       </c>
       <c r="B31" t="n">
-        <v>110378</v>
+        <v>4776</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4117,34 +4022,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219711</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697678</v>
+        <v>697616</v>
       </c>
       <c r="R31" t="n">
-        <v>6556802</v>
+        <v>6556904</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4176,7 +4086,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4186,7 +4096,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4197,6 +4107,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4213,10 +4143,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540896</v>
+        <v>122540881</v>
       </c>
       <c r="B32" t="n">
-        <v>110378</v>
+        <v>94761</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4229,21 +4159,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219711</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4253,13 +4183,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697607</v>
+        <v>697597</v>
       </c>
       <c r="R32" t="n">
-        <v>6556976</v>
+        <v>6556987</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4288,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4298,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4309,6 +4239,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4325,10 +4275,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540889</v>
+        <v>122540878</v>
       </c>
       <c r="B33" t="n">
-        <v>110378</v>
+        <v>8430</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4341,34 +4291,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697668</v>
+        <v>697600</v>
       </c>
       <c r="R33" t="n">
-        <v>6556773</v>
+        <v>6557016</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4400,7 +4355,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4410,7 +4365,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4421,6 +4376,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4437,10 +4412,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540886</v>
+        <v>122540897</v>
       </c>
       <c r="B34" t="n">
-        <v>98262</v>
+        <v>94857</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4453,27 +4428,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219862</v>
+        <v>210</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4482,10 +4461,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697681</v>
+        <v>697581</v>
       </c>
       <c r="R34" t="n">
-        <v>6556807</v>
+        <v>6556970</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4517,7 +4496,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4527,7 +4506,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4538,6 +4517,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4554,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540881</v>
+        <v>122540888</v>
       </c>
       <c r="B35" t="n">
-        <v>94761</v>
+        <v>100506</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4570,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4594,13 +4593,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697597</v>
+        <v>697678</v>
       </c>
       <c r="R35" t="n">
-        <v>6556987</v>
+        <v>6556802</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4629,7 +4628,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4639,7 +4638,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4650,26 +4649,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4686,10 +4665,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540890</v>
+        <v>122540884</v>
       </c>
       <c r="B36" t="n">
-        <v>110378</v>
+        <v>8441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4702,34 +4681,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697667</v>
+        <v>697609</v>
       </c>
       <c r="R36" t="n">
-        <v>6556761</v>
+        <v>6556889</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4761,7 +4745,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4771,7 +4755,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4782,6 +4766,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4798,10 +4797,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540891</v>
+        <v>122540895</v>
       </c>
       <c r="B37" t="n">
-        <v>98240</v>
+        <v>57399</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4810,35 +4809,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4847,10 +4842,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697667</v>
+        <v>697710</v>
       </c>
       <c r="R37" t="n">
-        <v>6556761</v>
+        <v>6556732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4882,7 +4877,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4892,7 +4887,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4919,10 +4919,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122540888</v>
+        <v>122540887</v>
       </c>
       <c r="B38" t="n">
-        <v>100506</v>
+        <v>110378</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4935,21 +4935,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540893</v>
+        <v>122540896</v>
       </c>
       <c r="B39" t="n">
-        <v>100506</v>
+        <v>110378</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5047,21 +5047,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697710</v>
+        <v>697607</v>
       </c>
       <c r="R39" t="n">
-        <v>6556732</v>
+        <v>6556976</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122310585</v>
+        <v>122311404</v>
       </c>
       <c r="B14" t="n">
-        <v>90853</v>
+        <v>110379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,48 +2064,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697618</v>
+        <v>697695</v>
       </c>
       <c r="R14" t="n">
-        <v>6556920</v>
+        <v>6556744</v>
       </c>
       <c r="S14" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122311010</v>
+        <v>122310983</v>
       </c>
       <c r="B15" t="n">
-        <v>110378</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,31 +2180,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2215,13 +2216,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697679</v>
+        <v>697700</v>
       </c>
       <c r="R15" t="n">
-        <v>6556777</v>
+        <v>6556781</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2250,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122310983</v>
+        <v>122310585</v>
       </c>
       <c r="B16" t="n">
-        <v>57399</v>
+        <v>90854</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2325,9 +2326,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697700</v>
+        <v>697618</v>
       </c>
       <c r="R16" t="n">
-        <v>6556781</v>
+        <v>6556920</v>
       </c>
       <c r="S16" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122309800</v>
+        <v>122311010</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>110379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,32 +2423,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2456,13 +2451,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697596</v>
+        <v>697679</v>
       </c>
       <c r="R17" t="n">
-        <v>6557005</v>
+        <v>6556777</v>
       </c>
       <c r="S17" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,7 +2526,7 @@
         <v>122310912</v>
       </c>
       <c r="B18" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2644,10 +2639,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122311404</v>
+        <v>122309800</v>
       </c>
       <c r="B19" t="n">
-        <v>110378</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,41 +2655,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697695</v>
+        <v>697596</v>
       </c>
       <c r="R19" t="n">
-        <v>6556744</v>
+        <v>6557005</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122323737</v>
+        <v>122323126</v>
       </c>
       <c r="B20" t="n">
-        <v>110378</v>
+        <v>110379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697676</v>
+        <v>697732</v>
       </c>
       <c r="R20" t="n">
-        <v>6556742</v>
+        <v>6556749</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122323126</v>
+        <v>122323326</v>
       </c>
       <c r="B21" t="n">
-        <v>110378</v>
+        <v>110379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697732</v>
+        <v>697701</v>
       </c>
       <c r="R21" t="n">
-        <v>6556749</v>
+        <v>6556732</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122324459</v>
+        <v>122323737</v>
       </c>
       <c r="B22" t="n">
-        <v>95011</v>
+        <v>110379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,34 +3000,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697641</v>
+        <v>697676</v>
       </c>
       <c r="R22" t="n">
-        <v>6556847</v>
+        <v>6556742</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122323326</v>
+        <v>122324705</v>
       </c>
       <c r="B23" t="n">
-        <v>110378</v>
+        <v>90854</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3108,41 +3108,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697701</v>
+        <v>697615</v>
       </c>
       <c r="R23" t="n">
-        <v>6556732</v>
+        <v>6556966</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122324705</v>
+        <v>122323928</v>
       </c>
       <c r="B24" t="n">
-        <v>90853</v>
+        <v>110379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3220,41 +3220,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697615</v>
+        <v>697678</v>
       </c>
       <c r="R24" t="n">
-        <v>6556966</v>
+        <v>6556740</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122323928</v>
+        <v>122324459</v>
       </c>
       <c r="B25" t="n">
-        <v>110378</v>
+        <v>95012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,34 +3336,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697678</v>
+        <v>697641</v>
       </c>
       <c r="R25" t="n">
-        <v>6556740</v>
+        <v>6556847</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540889</v>
+        <v>122540887</v>
       </c>
       <c r="B26" t="n">
-        <v>110378</v>
+        <v>110379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697668</v>
+        <v>697678</v>
       </c>
       <c r="R26" t="n">
-        <v>6556773</v>
+        <v>6556802</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540891</v>
+        <v>122540884</v>
       </c>
       <c r="B27" t="n">
-        <v>98240</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,35 +3556,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3593,10 +3589,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697667</v>
+        <v>697609</v>
       </c>
       <c r="R27" t="n">
-        <v>6556761</v>
+        <v>6556889</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3628,7 +3624,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3634,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3649,6 +3645,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3665,10 +3676,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540893</v>
+        <v>122540890</v>
       </c>
       <c r="B28" t="n">
-        <v>100506</v>
+        <v>110379</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3681,21 +3692,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3705,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697710</v>
+        <v>697667</v>
       </c>
       <c r="R28" t="n">
-        <v>6556732</v>
+        <v>6556761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3740,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3750,7 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3777,10 +3788,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540890</v>
+        <v>122540886</v>
       </c>
       <c r="B29" t="n">
-        <v>110378</v>
+        <v>98263</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3793,34 +3804,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697667</v>
+        <v>697681</v>
       </c>
       <c r="R29" t="n">
-        <v>6556761</v>
+        <v>6556807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3852,7 +3868,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3862,7 +3878,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3889,10 +3905,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540886</v>
+        <v>122540889</v>
       </c>
       <c r="B30" t="n">
-        <v>98262</v>
+        <v>110379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3905,39 +3921,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697681</v>
+        <v>697668</v>
       </c>
       <c r="R30" t="n">
-        <v>6556807</v>
+        <v>6556773</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3969,7 +3980,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3979,7 +3990,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4143,10 +4154,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540881</v>
+        <v>122540897</v>
       </c>
       <c r="B32" t="n">
-        <v>94761</v>
+        <v>94858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4159,37 +4170,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697597</v>
+        <v>697581</v>
       </c>
       <c r="R32" t="n">
-        <v>6556987</v>
+        <v>6556970</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4218,7 +4238,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4228,7 +4248,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4242,22 +4262,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
+          <t>Tallågor i stockbro över skogsbäck.</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4412,10 +4432,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540897</v>
+        <v>122540891</v>
       </c>
       <c r="B34" t="n">
-        <v>94857</v>
+        <v>98241</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4424,35 +4444,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4461,10 +4481,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697581</v>
+        <v>697667</v>
       </c>
       <c r="R34" t="n">
-        <v>6556970</v>
+        <v>6556761</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4496,7 +4516,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4506,7 +4526,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,26 +4537,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540888</v>
+        <v>122540896</v>
       </c>
       <c r="B35" t="n">
-        <v>100506</v>
+        <v>110379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697678</v>
+        <v>697607</v>
       </c>
       <c r="R35" t="n">
-        <v>6556802</v>
+        <v>6556976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4665,10 +4665,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540884</v>
+        <v>122540895</v>
       </c>
       <c r="B36" t="n">
-        <v>8441</v>
+        <v>57400</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4677,31 +4677,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697609</v>
+        <v>697710</v>
       </c>
       <c r="R36" t="n">
-        <v>6556889</v>
+        <v>6556732</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4755,7 +4755,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4766,21 +4771,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4797,10 +4787,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540895</v>
+        <v>122540893</v>
       </c>
       <c r="B37" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4809,33 +4799,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
@@ -4877,7 +4862,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4887,12 +4872,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4919,10 +4899,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122540887</v>
+        <v>122540888</v>
       </c>
       <c r="B38" t="n">
-        <v>110378</v>
+        <v>100507</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4935,21 +4915,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5031,10 +5011,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540896</v>
+        <v>122540881</v>
       </c>
       <c r="B39" t="n">
-        <v>110378</v>
+        <v>94762</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5047,21 +5027,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219711</v>
+        <v>2818</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5071,13 +5051,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697607</v>
+        <v>697597</v>
       </c>
       <c r="R39" t="n">
-        <v>6556976</v>
+        <v>6556987</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5106,7 +5086,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5116,7 +5096,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5127,6 +5107,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5146,7 +5146,7 @@
         <v>122540898</v>
       </c>
       <c r="B40" t="n">
-        <v>94857</v>
+        <v>94858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>122540885</v>
       </c>
       <c r="B41" t="n">
-        <v>94904</v>
+        <v>94905</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>122540882</v>
       </c>
       <c r="B42" t="n">
-        <v>96305</v>
+        <v>96306</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122323928</v>
+        <v>122324459</v>
       </c>
       <c r="B24" t="n">
-        <v>110379</v>
+        <v>95012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,34 +3224,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697678</v>
+        <v>697641</v>
       </c>
       <c r="R24" t="n">
-        <v>6556740</v>
+        <v>6556847</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122324459</v>
+        <v>122323928</v>
       </c>
       <c r="B25" t="n">
-        <v>95012</v>
+        <v>110379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,34 +3336,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697641</v>
+        <v>697678</v>
       </c>
       <c r="R25" t="n">
-        <v>6556847</v>
+        <v>6556740</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122311404</v>
+        <v>122310912</v>
       </c>
       <c r="B14" t="n">
-        <v>110379</v>
+        <v>100510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,17 +2092,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697695</v>
+        <v>697686</v>
       </c>
       <c r="R14" t="n">
-        <v>6556744</v>
+        <v>6556802</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122310983</v>
+        <v>122309800</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,25 +2180,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2206,6 +2206,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -2216,13 +2217,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697700</v>
+        <v>697596</v>
       </c>
       <c r="R15" t="n">
-        <v>6556781</v>
+        <v>6557005</v>
       </c>
       <c r="S15" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,7 +2292,7 @@
         <v>122310585</v>
       </c>
       <c r="B16" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2407,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122311010</v>
+        <v>122310983</v>
       </c>
       <c r="B17" t="n">
-        <v>110379</v>
+        <v>57400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,31 +2420,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2451,13 +2456,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697679</v>
+        <v>697700</v>
       </c>
       <c r="R17" t="n">
-        <v>6556777</v>
+        <v>6556781</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2528,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122310912</v>
+        <v>122311010</v>
       </c>
       <c r="B18" t="n">
-        <v>100507</v>
+        <v>110382</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,21 +2544,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2567,13 +2572,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697686</v>
+        <v>697679</v>
       </c>
       <c r="R18" t="n">
-        <v>6556802</v>
+        <v>6556777</v>
       </c>
       <c r="S18" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2602,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122309800</v>
+        <v>122311404</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>110382</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2655,46 +2660,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697596</v>
+        <v>697695</v>
       </c>
       <c r="R19" t="n">
-        <v>6557005</v>
+        <v>6556744</v>
       </c>
       <c r="S19" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122323126</v>
+        <v>122324459</v>
       </c>
       <c r="B20" t="n">
-        <v>110379</v>
+        <v>95015</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2776,34 +2776,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697732</v>
+        <v>697641</v>
       </c>
       <c r="R20" t="n">
-        <v>6556749</v>
+        <v>6556847</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2875,7 +2875,7 @@
         <v>122323326</v>
       </c>
       <c r="B21" t="n">
-        <v>110379</v>
+        <v>110382</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122323737</v>
+        <v>122323928</v>
       </c>
       <c r="B22" t="n">
-        <v>110379</v>
+        <v>110382</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697676</v>
+        <v>697678</v>
       </c>
       <c r="R22" t="n">
-        <v>6556742</v>
+        <v>6556740</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122324705</v>
+        <v>122323737</v>
       </c>
       <c r="B23" t="n">
-        <v>90854</v>
+        <v>110382</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3108,41 +3108,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697615</v>
+        <v>697676</v>
       </c>
       <c r="R23" t="n">
-        <v>6556966</v>
+        <v>6556742</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122324459</v>
+        <v>122323126</v>
       </c>
       <c r="B24" t="n">
-        <v>95012</v>
+        <v>110382</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,34 +3224,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697641</v>
+        <v>697732</v>
       </c>
       <c r="R24" t="n">
-        <v>6556847</v>
+        <v>6556749</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122323928</v>
+        <v>122324705</v>
       </c>
       <c r="B25" t="n">
-        <v>110379</v>
+        <v>90857</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,41 +3332,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697678</v>
+        <v>697615</v>
       </c>
       <c r="R25" t="n">
-        <v>6556740</v>
+        <v>6556966</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540887</v>
+        <v>122540895</v>
       </c>
       <c r="B26" t="n">
-        <v>110379</v>
+        <v>57400</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3444,38 +3444,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697678</v>
+        <v>697710</v>
       </c>
       <c r="R26" t="n">
-        <v>6556802</v>
+        <v>6556732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3522,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,10 +3554,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540884</v>
+        <v>122540878</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3560,21 +3570,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3589,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697609</v>
+        <v>697600</v>
       </c>
       <c r="R27" t="n">
-        <v>6556889</v>
+        <v>6557016</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3624,7 +3634,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3634,7 +3644,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3648,17 +3658,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula # Barklös björklåga.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3676,10 +3691,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540890</v>
+        <v>122540889</v>
       </c>
       <c r="B28" t="n">
-        <v>110379</v>
+        <v>110382</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3716,10 +3731,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697667</v>
+        <v>697668</v>
       </c>
       <c r="R28" t="n">
-        <v>6556761</v>
+        <v>6556773</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3751,7 +3766,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3776,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,10 +3803,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540886</v>
+        <v>122540891</v>
       </c>
       <c r="B29" t="n">
-        <v>98263</v>
+        <v>98244</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3800,31 +3815,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219862</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3833,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697681</v>
+        <v>697667</v>
       </c>
       <c r="R29" t="n">
-        <v>6556807</v>
+        <v>6556761</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3868,7 +3887,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3878,7 +3897,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3905,10 +3924,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540889</v>
+        <v>122540887</v>
       </c>
       <c r="B30" t="n">
-        <v>110379</v>
+        <v>110382</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3945,10 +3964,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697668</v>
+        <v>697678</v>
       </c>
       <c r="R30" t="n">
-        <v>6556773</v>
+        <v>6556802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3980,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3990,7 +4009,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4017,10 +4036,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540883</v>
+        <v>122540888</v>
       </c>
       <c r="B31" t="n">
-        <v>4776</v>
+        <v>100510</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4033,39 +4052,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697616</v>
+        <v>697678</v>
       </c>
       <c r="R31" t="n">
-        <v>6556904</v>
+        <v>6556802</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4097,7 +4111,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4107,7 +4121,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4118,26 +4132,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4154,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540897</v>
+        <v>122540883</v>
       </c>
       <c r="B32" t="n">
-        <v>94858</v>
+        <v>4776</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4170,31 +4164,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>210</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4203,10 +4193,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697581</v>
+        <v>697616</v>
       </c>
       <c r="R32" t="n">
-        <v>6556970</v>
+        <v>6556904</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4238,7 +4228,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4248,7 +4238,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4262,22 +4252,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4295,10 +4285,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540878</v>
+        <v>122540890</v>
       </c>
       <c r="B33" t="n">
-        <v>8430</v>
+        <v>110382</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4311,39 +4301,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106554</v>
+        <v>219711</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697600</v>
+        <v>697667</v>
       </c>
       <c r="R33" t="n">
-        <v>6557016</v>
+        <v>6556761</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4375,7 +4360,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4385,7 +4370,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4396,26 +4381,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Betula # Barklös björklåga.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4432,10 +4397,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540891</v>
+        <v>122540896</v>
       </c>
       <c r="B34" t="n">
-        <v>98241</v>
+        <v>110382</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4444,47 +4409,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697667</v>
+        <v>697607</v>
       </c>
       <c r="R34" t="n">
-        <v>6556761</v>
+        <v>6556976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4516,7 +4472,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4526,7 +4482,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4553,10 +4509,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540896</v>
+        <v>122540886</v>
       </c>
       <c r="B35" t="n">
-        <v>110379</v>
+        <v>98266</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,34 +4525,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697607</v>
+        <v>697681</v>
       </c>
       <c r="R35" t="n">
-        <v>6556976</v>
+        <v>6556807</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4628,7 +4589,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4638,7 +4599,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4665,10 +4626,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540895</v>
+        <v>122540897</v>
       </c>
       <c r="B36" t="n">
-        <v>57400</v>
+        <v>94861</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4677,31 +4638,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4710,10 +4675,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697710</v>
+        <v>697581</v>
       </c>
       <c r="R36" t="n">
-        <v>6556732</v>
+        <v>6556970</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4745,7 +4710,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4755,12 +4720,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4771,6 +4731,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4787,10 +4767,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540893</v>
+        <v>122540884</v>
       </c>
       <c r="B37" t="n">
-        <v>100507</v>
+        <v>8441</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4803,34 +4783,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697710</v>
+        <v>697609</v>
       </c>
       <c r="R37" t="n">
-        <v>6556732</v>
+        <v>6556889</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4862,7 +4847,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4872,7 +4857,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4883,6 +4868,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4899,10 +4899,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122540888</v>
+        <v>122540893</v>
       </c>
       <c r="B38" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697678</v>
+        <v>697710</v>
       </c>
       <c r="R38" t="n">
-        <v>6556802</v>
+        <v>6556732</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5014,7 +5014,7 @@
         <v>122540881</v>
       </c>
       <c r="B39" t="n">
-        <v>94762</v>
+        <v>94765</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5143,10 +5143,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122540898</v>
+        <v>122540885</v>
       </c>
       <c r="B40" t="n">
-        <v>94858</v>
+        <v>94908</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5159,43 +5159,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>210</v>
+        <v>2170</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697586</v>
+        <v>697628</v>
       </c>
       <c r="R40" t="n">
-        <v>6556969</v>
+        <v>6556873</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5227,7 +5218,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5237,7 +5228,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5248,26 +5239,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5284,10 +5255,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122540885</v>
+        <v>122540898</v>
       </c>
       <c r="B41" t="n">
-        <v>94905</v>
+        <v>94861</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5300,34 +5271,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2170</v>
+        <v>210</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>697628</v>
+        <v>697586</v>
       </c>
       <c r="R41" t="n">
-        <v>6556873</v>
+        <v>6556969</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5359,7 +5339,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5369,7 +5349,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5380,6 +5360,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5399,7 +5399,7 @@
         <v>122540882</v>
       </c>
       <c r="B42" t="n">
-        <v>96306</v>
+        <v>96309</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -2052,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122310912</v>
+        <v>122310983</v>
       </c>
       <c r="B14" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,31 +2064,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2096,13 +2100,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697686</v>
+        <v>697700</v>
       </c>
       <c r="R14" t="n">
-        <v>6556802</v>
+        <v>6556781</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122309800</v>
+        <v>122311404</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>110382</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,46 +2188,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandtäppan, Srm</t>
+          <t>Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697596</v>
+        <v>697695</v>
       </c>
       <c r="R15" t="n">
-        <v>6557005</v>
+        <v>6556744</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2252,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,10 +2407,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122310983</v>
+        <v>122311010</v>
       </c>
       <c r="B17" t="n">
-        <v>57400</v>
+        <v>110382</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,35 +2419,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2456,13 +2451,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697700</v>
+        <v>697679</v>
       </c>
       <c r="R17" t="n">
-        <v>6556781</v>
+        <v>6556777</v>
       </c>
       <c r="S17" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2528,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122311010</v>
+        <v>122309800</v>
       </c>
       <c r="B18" t="n">
-        <v>110382</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,27 +2539,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697679</v>
+        <v>697596</v>
       </c>
       <c r="R18" t="n">
-        <v>6556777</v>
+        <v>6557005</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122311404</v>
+        <v>122310912</v>
       </c>
       <c r="B19" t="n">
-        <v>110382</v>
+        <v>100510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,21 +2660,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2684,17 +2684,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hemträsket, Srm</t>
+          <t>Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697695</v>
+        <v>697686</v>
       </c>
       <c r="R19" t="n">
-        <v>6556744</v>
+        <v>6556802</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122324459</v>
+        <v>122323326</v>
       </c>
       <c r="B20" t="n">
-        <v>95015</v>
+        <v>110382</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2776,34 +2776,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697641</v>
+        <v>697701</v>
       </c>
       <c r="R20" t="n">
-        <v>6556847</v>
+        <v>6556732</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,7 +2872,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122323326</v>
+        <v>122323928</v>
       </c>
       <c r="B21" t="n">
         <v>110382</v>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697701</v>
+        <v>697678</v>
       </c>
       <c r="R21" t="n">
-        <v>6556732</v>
+        <v>6556740</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122323928</v>
+        <v>122324705</v>
       </c>
       <c r="B22" t="n">
-        <v>110382</v>
+        <v>90857</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2996,41 +2996,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697678</v>
+        <v>697615</v>
       </c>
       <c r="R22" t="n">
-        <v>6556740</v>
+        <v>6556966</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122323737</v>
+        <v>122323126</v>
       </c>
       <c r="B23" t="n">
         <v>110382</v>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697676</v>
+        <v>697732</v>
       </c>
       <c r="R23" t="n">
-        <v>6556742</v>
+        <v>6556749</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122323126</v>
+        <v>122324459</v>
       </c>
       <c r="B24" t="n">
-        <v>110382</v>
+        <v>95015</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,34 +3224,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hemträsket, Hemträsket, Srm</t>
+          <t>Sandtäppan, Sandtäppan, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697732</v>
+        <v>697641</v>
       </c>
       <c r="R24" t="n">
-        <v>6556749</v>
+        <v>6556847</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122324705</v>
+        <v>122323737</v>
       </c>
       <c r="B25" t="n">
-        <v>90857</v>
+        <v>110382</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,41 +3332,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandtäppan, Sandtäppan, Srm</t>
+          <t>Hemträsket, Hemträsket, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697615</v>
+        <v>697676</v>
       </c>
       <c r="R25" t="n">
-        <v>6556966</v>
+        <v>6556742</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540895</v>
+        <v>122540887</v>
       </c>
       <c r="B26" t="n">
-        <v>57400</v>
+        <v>110382</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3444,43 +3444,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697710</v>
+        <v>697678</v>
       </c>
       <c r="R26" t="n">
-        <v>6556732</v>
+        <v>6556802</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3512,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3522,12 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540878</v>
+        <v>122540886</v>
       </c>
       <c r="B27" t="n">
-        <v>8430</v>
+        <v>98266</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3570,27 +3560,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106554</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3599,10 +3589,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697600</v>
+        <v>697681</v>
       </c>
       <c r="R27" t="n">
-        <v>6557016</v>
+        <v>6556807</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3634,7 +3624,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3644,7 +3634,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3655,26 +3645,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Betula # Barklös björklåga.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3691,10 +3661,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540889</v>
+        <v>122540878</v>
       </c>
       <c r="B28" t="n">
-        <v>110382</v>
+        <v>8430</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3707,34 +3677,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697668</v>
+        <v>697600</v>
       </c>
       <c r="R28" t="n">
-        <v>6556773</v>
+        <v>6557016</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3766,7 +3741,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3776,7 +3751,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3787,6 +3762,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3803,10 +3798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540891</v>
+        <v>122540883</v>
       </c>
       <c r="B29" t="n">
-        <v>98244</v>
+        <v>4776</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3815,35 +3810,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3852,10 +3843,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697667</v>
+        <v>697616</v>
       </c>
       <c r="R29" t="n">
-        <v>6556761</v>
+        <v>6556904</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3887,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3897,7 +3888,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3908,6 +3899,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3924,10 +3935,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540887</v>
+        <v>122540895</v>
       </c>
       <c r="B30" t="n">
-        <v>110382</v>
+        <v>57400</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3936,38 +3947,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697678</v>
+        <v>697710</v>
       </c>
       <c r="R30" t="n">
-        <v>6556802</v>
+        <v>6556732</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3999,7 +4015,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,7 +4025,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4036,10 +4057,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540888</v>
+        <v>122540884</v>
       </c>
       <c r="B31" t="n">
-        <v>100510</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4052,34 +4073,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697678</v>
+        <v>697609</v>
       </c>
       <c r="R31" t="n">
-        <v>6556802</v>
+        <v>6556889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4111,7 +4137,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4121,7 +4147,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4132,6 +4158,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4148,10 +4189,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540883</v>
+        <v>122540891</v>
       </c>
       <c r="B32" t="n">
-        <v>4776</v>
+        <v>98244</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4160,31 +4201,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4193,10 +4238,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697616</v>
+        <v>697667</v>
       </c>
       <c r="R32" t="n">
-        <v>6556904</v>
+        <v>6556761</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4228,7 +4273,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4238,7 +4283,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4249,26 +4294,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4285,10 +4310,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540890</v>
+        <v>122540881</v>
       </c>
       <c r="B33" t="n">
-        <v>110382</v>
+        <v>94765</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4301,21 +4326,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219711</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4325,13 +4350,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697667</v>
+        <v>697597</v>
       </c>
       <c r="R33" t="n">
-        <v>6556761</v>
+        <v>6556987</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4360,7 +4385,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4370,7 +4395,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4381,6 +4406,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4397,7 +4442,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540896</v>
+        <v>122540889</v>
       </c>
       <c r="B34" t="n">
         <v>110382</v>
@@ -4437,10 +4482,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697607</v>
+        <v>697668</v>
       </c>
       <c r="R34" t="n">
-        <v>6556976</v>
+        <v>6556773</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4472,7 +4517,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4482,7 +4527,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4509,10 +4554,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540886</v>
+        <v>122540888</v>
       </c>
       <c r="B35" t="n">
-        <v>98266</v>
+        <v>100510</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4525,39 +4570,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697681</v>
+        <v>697678</v>
       </c>
       <c r="R35" t="n">
-        <v>6556807</v>
+        <v>6556802</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4589,7 +4629,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4599,7 +4639,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4767,10 +4807,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540884</v>
+        <v>122540890</v>
       </c>
       <c r="B37" t="n">
-        <v>8441</v>
+        <v>110382</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4783,39 +4823,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697609</v>
+        <v>697667</v>
       </c>
       <c r="R37" t="n">
-        <v>6556889</v>
+        <v>6556761</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4847,7 +4882,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4857,7 +4892,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4868,21 +4903,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5011,10 +5031,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540881</v>
+        <v>122540896</v>
       </c>
       <c r="B39" t="n">
-        <v>94765</v>
+        <v>110382</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5027,21 +5047,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>219711</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5051,13 +5071,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697597</v>
+        <v>697607</v>
       </c>
       <c r="R39" t="n">
-        <v>6556987</v>
+        <v>6556976</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5086,7 +5106,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5096,7 +5116,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5107,26 +5127,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -4442,10 +4442,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540889</v>
+        <v>122540888</v>
       </c>
       <c r="B34" t="n">
-        <v>110382</v>
+        <v>100510</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4458,21 +4458,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697668</v>
+        <v>697678</v>
       </c>
       <c r="R34" t="n">
-        <v>6556773</v>
+        <v>6556802</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4554,10 +4554,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540888</v>
+        <v>122540889</v>
       </c>
       <c r="B35" t="n">
-        <v>100510</v>
+        <v>110382</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697678</v>
+        <v>697668</v>
       </c>
       <c r="R35" t="n">
-        <v>6556802</v>
+        <v>6556773</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -4442,10 +4442,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540888</v>
+        <v>122540889</v>
       </c>
       <c r="B34" t="n">
-        <v>100510</v>
+        <v>110382</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4458,21 +4458,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697678</v>
+        <v>697668</v>
       </c>
       <c r="R34" t="n">
-        <v>6556802</v>
+        <v>6556773</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4554,10 +4554,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540889</v>
+        <v>122540888</v>
       </c>
       <c r="B35" t="n">
-        <v>110382</v>
+        <v>100510</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697668</v>
+        <v>697678</v>
       </c>
       <c r="R35" t="n">
-        <v>6556773</v>
+        <v>6556802</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540887</v>
+        <v>122540878</v>
       </c>
       <c r="B26" t="n">
-        <v>110382</v>
+        <v>8430</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,34 +3448,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697678</v>
+        <v>697600</v>
       </c>
       <c r="R26" t="n">
-        <v>6556802</v>
+        <v>6557016</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,6 +3533,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3544,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540886</v>
+        <v>122540895</v>
       </c>
       <c r="B27" t="n">
-        <v>98266</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,31 +3581,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219862</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3589,10 +3614,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697681</v>
+        <v>697710</v>
       </c>
       <c r="R27" t="n">
-        <v>6556807</v>
+        <v>6556732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3624,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3634,7 +3659,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,10 +3691,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540878</v>
+        <v>122540888</v>
       </c>
       <c r="B28" t="n">
-        <v>8430</v>
+        <v>100613</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3677,39 +3707,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697600</v>
+        <v>697678</v>
       </c>
       <c r="R28" t="n">
-        <v>6557016</v>
+        <v>6556802</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3741,7 +3766,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3751,7 +3776,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3762,26 +3787,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Betula # Barklös björklåga.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3798,10 +3803,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540883</v>
+        <v>122540890</v>
       </c>
       <c r="B29" t="n">
-        <v>4776</v>
+        <v>110485</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3814,39 +3819,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102306</v>
+        <v>219711</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697616</v>
+        <v>697667</v>
       </c>
       <c r="R29" t="n">
-        <v>6556904</v>
+        <v>6556761</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3899,26 +3899,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3935,10 +3915,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540895</v>
+        <v>122540887</v>
       </c>
       <c r="B30" t="n">
-        <v>57400</v>
+        <v>110485</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3947,43 +3927,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697710</v>
+        <v>697678</v>
       </c>
       <c r="R30" t="n">
-        <v>6556732</v>
+        <v>6556802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4015,7 +3990,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4025,12 +4000,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4057,10 +4027,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540884</v>
+        <v>122540886</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>98369</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4073,27 +4043,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>219862</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4102,10 +4072,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697609</v>
+        <v>697681</v>
       </c>
       <c r="R31" t="n">
-        <v>6556889</v>
+        <v>6556807</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4137,7 +4107,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4147,7 +4117,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4158,21 +4128,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4189,10 +4144,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540891</v>
+        <v>122540884</v>
       </c>
       <c r="B32" t="n">
-        <v>98244</v>
+        <v>8441</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4201,35 +4156,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4238,10 +4189,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697667</v>
+        <v>697609</v>
       </c>
       <c r="R32" t="n">
-        <v>6556761</v>
+        <v>6556889</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4273,7 +4224,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4283,7 +4234,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4294,6 +4245,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4310,10 +4276,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540881</v>
+        <v>122540897</v>
       </c>
       <c r="B33" t="n">
-        <v>94765</v>
+        <v>94964</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4326,37 +4292,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697597</v>
+        <v>697581</v>
       </c>
       <c r="R33" t="n">
-        <v>6556987</v>
+        <v>6556970</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4385,7 +4360,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4395,7 +4370,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4409,22 +4384,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
+          <t>Tallågor i stockbro över skogsbäck.</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4442,10 +4417,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540889</v>
+        <v>122540881</v>
       </c>
       <c r="B34" t="n">
-        <v>110382</v>
+        <v>94868</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4458,21 +4433,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219711</v>
+        <v>2818</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4482,13 +4457,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697668</v>
+        <v>697597</v>
       </c>
       <c r="R34" t="n">
-        <v>6556773</v>
+        <v>6556987</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4517,7 +4492,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4527,7 +4502,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4538,6 +4513,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4554,10 +4549,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540888</v>
+        <v>122540883</v>
       </c>
       <c r="B35" t="n">
-        <v>100510</v>
+        <v>4776</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4570,34 +4565,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697678</v>
+        <v>697616</v>
       </c>
       <c r="R35" t="n">
-        <v>6556802</v>
+        <v>6556904</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4650,6 +4650,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4666,10 +4686,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540897</v>
+        <v>122540891</v>
       </c>
       <c r="B36" t="n">
-        <v>94861</v>
+        <v>98347</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4678,35 +4698,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4715,10 +4735,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697581</v>
+        <v>697667</v>
       </c>
       <c r="R36" t="n">
-        <v>6556970</v>
+        <v>6556761</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4750,7 +4770,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4760,7 +4780,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4771,26 +4791,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4807,10 +4807,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540890</v>
+        <v>122540889</v>
       </c>
       <c r="B37" t="n">
-        <v>110382</v>
+        <v>110485</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697667</v>
+        <v>697668</v>
       </c>
       <c r="R37" t="n">
-        <v>6556761</v>
+        <v>6556773</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4922,7 +4922,7 @@
         <v>122540893</v>
       </c>
       <c r="B38" t="n">
-        <v>100510</v>
+        <v>100613</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>122540896</v>
       </c>
       <c r="B39" t="n">
-        <v>110382</v>
+        <v>110485</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>122540885</v>
       </c>
       <c r="B40" t="n">
-        <v>94908</v>
+        <v>95011</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>122540898</v>
       </c>
       <c r="B41" t="n">
-        <v>94861</v>
+        <v>94964</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>122540882</v>
       </c>
       <c r="B42" t="n">
-        <v>96309</v>
+        <v>96412</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540878</v>
+        <v>122540889</v>
       </c>
       <c r="B26" t="n">
-        <v>8430</v>
+        <v>110493</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,39 +3448,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697600</v>
+        <v>697668</v>
       </c>
       <c r="R26" t="n">
-        <v>6557016</v>
+        <v>6556773</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3512,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3522,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,26 +3528,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Betula # Barklös björklåga.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3569,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540895</v>
+        <v>122540897</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>94972</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,31 +3556,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3614,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697710</v>
+        <v>697581</v>
       </c>
       <c r="R27" t="n">
-        <v>6556732</v>
+        <v>6556970</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3649,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,12 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3675,6 +3649,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3691,10 +3685,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540888</v>
+        <v>122540890</v>
       </c>
       <c r="B28" t="n">
-        <v>100613</v>
+        <v>110493</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3707,21 +3701,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3731,10 +3725,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697678</v>
+        <v>697667</v>
       </c>
       <c r="R28" t="n">
-        <v>6556802</v>
+        <v>6556761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3766,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3776,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3803,10 +3797,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540890</v>
+        <v>122540886</v>
       </c>
       <c r="B29" t="n">
-        <v>110485</v>
+        <v>98377</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3819,34 +3813,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697667</v>
+        <v>697681</v>
       </c>
       <c r="R29" t="n">
-        <v>6556761</v>
+        <v>6556807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3878,7 +3877,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3888,7 +3887,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3915,10 +3914,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540887</v>
+        <v>122540878</v>
       </c>
       <c r="B30" t="n">
-        <v>110485</v>
+        <v>8430</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3931,34 +3930,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697678</v>
+        <v>697600</v>
       </c>
       <c r="R30" t="n">
-        <v>6556802</v>
+        <v>6557016</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3990,7 +3994,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4000,7 +4004,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4011,6 +4015,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4027,10 +4051,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540886</v>
+        <v>122540895</v>
       </c>
       <c r="B31" t="n">
-        <v>98369</v>
+        <v>57494</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4039,31 +4063,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219862</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4072,10 +4096,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697681</v>
+        <v>697710</v>
       </c>
       <c r="R31" t="n">
-        <v>6556807</v>
+        <v>6556732</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4107,7 +4131,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4117,7 +4141,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4144,10 +4173,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540884</v>
+        <v>122540896</v>
       </c>
       <c r="B32" t="n">
-        <v>8441</v>
+        <v>110493</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4160,39 +4189,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697609</v>
+        <v>697607</v>
       </c>
       <c r="R32" t="n">
-        <v>6556889</v>
+        <v>6556976</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,7 +4248,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4234,7 +4258,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4245,21 +4269,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4276,10 +4285,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540897</v>
+        <v>122540883</v>
       </c>
       <c r="B33" t="n">
-        <v>94964</v>
+        <v>4776</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4292,31 +4301,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>210</v>
+        <v>102306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4325,10 +4330,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697581</v>
+        <v>697616</v>
       </c>
       <c r="R33" t="n">
-        <v>6556970</v>
+        <v>6556904</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4360,7 +4365,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4370,7 +4375,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4384,22 +4389,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4420,7 +4425,7 @@
         <v>122540881</v>
       </c>
       <c r="B34" t="n">
-        <v>94868</v>
+        <v>94876</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4549,10 +4554,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540883</v>
+        <v>122540887</v>
       </c>
       <c r="B35" t="n">
-        <v>4776</v>
+        <v>110493</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4565,39 +4570,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102306</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697616</v>
+        <v>697678</v>
       </c>
       <c r="R35" t="n">
-        <v>6556904</v>
+        <v>6556802</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4650,26 +4650,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4686,10 +4666,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540891</v>
+        <v>122540893</v>
       </c>
       <c r="B36" t="n">
-        <v>98347</v>
+        <v>100621</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4698,47 +4678,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697667</v>
+        <v>697710</v>
       </c>
       <c r="R36" t="n">
-        <v>6556761</v>
+        <v>6556732</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4770,7 +4741,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4780,7 +4751,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4807,10 +4778,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540889</v>
+        <v>122540888</v>
       </c>
       <c r="B37" t="n">
-        <v>110485</v>
+        <v>100621</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4823,21 +4794,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4847,10 +4818,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697668</v>
+        <v>697678</v>
       </c>
       <c r="R37" t="n">
-        <v>6556773</v>
+        <v>6556802</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4882,7 +4853,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4892,7 +4863,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4919,10 +4890,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122540893</v>
+        <v>122540884</v>
       </c>
       <c r="B38" t="n">
-        <v>100613</v>
+        <v>8441</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4935,34 +4906,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697710</v>
+        <v>697609</v>
       </c>
       <c r="R38" t="n">
-        <v>6556732</v>
+        <v>6556889</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4994,7 +4970,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5004,7 +4980,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5015,6 +4991,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5031,10 +5022,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540896</v>
+        <v>122540891</v>
       </c>
       <c r="B39" t="n">
-        <v>110485</v>
+        <v>98355</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5043,38 +5034,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697607</v>
+        <v>697667</v>
       </c>
       <c r="R39" t="n">
-        <v>6556976</v>
+        <v>6556761</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5146,7 +5146,7 @@
         <v>122540885</v>
       </c>
       <c r="B40" t="n">
-        <v>95011</v>
+        <v>95019</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>122540898</v>
       </c>
       <c r="B41" t="n">
-        <v>94964</v>
+        <v>94972</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>122540882</v>
       </c>
       <c r="B42" t="n">
-        <v>96412</v>
+        <v>96420</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540889</v>
+        <v>122540883</v>
       </c>
       <c r="B26" t="n">
-        <v>110493</v>
+        <v>4776</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,34 +3448,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>102306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697668</v>
+        <v>697616</v>
       </c>
       <c r="R26" t="n">
-        <v>6556773</v>
+        <v>6556904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,6 +3533,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3544,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540897</v>
+        <v>122540887</v>
       </c>
       <c r="B27" t="n">
-        <v>94972</v>
+        <v>110493</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3560,43 +3585,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697581</v>
+        <v>697678</v>
       </c>
       <c r="R27" t="n">
-        <v>6556970</v>
+        <v>6556802</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3628,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3649,26 +3665,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3685,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540890</v>
+        <v>122540886</v>
       </c>
       <c r="B28" t="n">
-        <v>110493</v>
+        <v>98377</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3701,34 +3697,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697667</v>
+        <v>697681</v>
       </c>
       <c r="R28" t="n">
-        <v>6556761</v>
+        <v>6556807</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3771,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3797,10 +3798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540886</v>
+        <v>122540897</v>
       </c>
       <c r="B29" t="n">
-        <v>98377</v>
+        <v>94972</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3813,27 +3814,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219862</v>
+        <v>210</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3842,10 +3847,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697681</v>
+        <v>697581</v>
       </c>
       <c r="R29" t="n">
-        <v>6556807</v>
+        <v>6556970</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3877,7 +3882,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3887,7 +3892,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3898,6 +3903,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3914,10 +3939,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540878</v>
+        <v>122540888</v>
       </c>
       <c r="B30" t="n">
-        <v>8430</v>
+        <v>100621</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3930,39 +3955,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697600</v>
+        <v>697678</v>
       </c>
       <c r="R30" t="n">
-        <v>6557016</v>
+        <v>6556802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3994,7 +4014,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4004,7 +4024,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4015,26 +4035,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Betula # Barklös björklåga.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4051,10 +4051,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540895</v>
+        <v>122540896</v>
       </c>
       <c r="B31" t="n">
-        <v>57494</v>
+        <v>110493</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4063,43 +4063,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697710</v>
+        <v>697607</v>
       </c>
       <c r="R31" t="n">
-        <v>6556732</v>
+        <v>6556976</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4131,7 +4126,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4141,12 +4136,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4173,10 +4163,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540896</v>
+        <v>122540891</v>
       </c>
       <c r="B32" t="n">
-        <v>110493</v>
+        <v>98355</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4185,38 +4175,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697607</v>
+        <v>697667</v>
       </c>
       <c r="R32" t="n">
-        <v>6556976</v>
+        <v>6556761</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4248,7 +4247,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4258,7 +4257,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4285,10 +4284,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540883</v>
+        <v>122540893</v>
       </c>
       <c r="B33" t="n">
-        <v>4776</v>
+        <v>100621</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4301,39 +4300,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697616</v>
+        <v>697710</v>
       </c>
       <c r="R33" t="n">
-        <v>6556904</v>
+        <v>6556732</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4365,7 +4359,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4375,7 +4369,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4386,26 +4380,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4422,10 +4396,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540881</v>
+        <v>122540890</v>
       </c>
       <c r="B34" t="n">
-        <v>94876</v>
+        <v>110493</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4438,21 +4412,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2818</v>
+        <v>219711</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4462,13 +4436,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697597</v>
+        <v>697667</v>
       </c>
       <c r="R34" t="n">
-        <v>6556987</v>
+        <v>6556761</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4497,7 +4471,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4507,7 +4481,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4518,26 +4492,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4554,10 +4508,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540887</v>
+        <v>122540878</v>
       </c>
       <c r="B35" t="n">
-        <v>110493</v>
+        <v>8430</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4570,34 +4524,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697678</v>
+        <v>697600</v>
       </c>
       <c r="R35" t="n">
-        <v>6556802</v>
+        <v>6557016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4629,7 +4588,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4639,7 +4598,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4650,6 +4609,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4666,10 +4645,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540893</v>
+        <v>122540889</v>
       </c>
       <c r="B36" t="n">
-        <v>100621</v>
+        <v>110493</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4682,21 +4661,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4706,10 +4685,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697710</v>
+        <v>697668</v>
       </c>
       <c r="R36" t="n">
-        <v>6556732</v>
+        <v>6556773</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4741,7 +4720,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4751,7 +4730,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4778,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540888</v>
+        <v>122540884</v>
       </c>
       <c r="B37" t="n">
-        <v>100621</v>
+        <v>8441</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4794,34 +4773,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697678</v>
+        <v>697609</v>
       </c>
       <c r="R37" t="n">
-        <v>6556802</v>
+        <v>6556889</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4853,7 +4837,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4863,7 +4847,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4874,6 +4858,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4890,10 +4889,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122540884</v>
+        <v>122540895</v>
       </c>
       <c r="B38" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4902,31 +4901,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4935,10 +4934,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697609</v>
+        <v>697710</v>
       </c>
       <c r="R38" t="n">
-        <v>6556889</v>
+        <v>6556732</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,7 +4969,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4980,7 +4979,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4991,21 +4995,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5022,10 +5011,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540891</v>
+        <v>122540881</v>
       </c>
       <c r="B39" t="n">
-        <v>98355</v>
+        <v>94876</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5034,50 +5023,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697667</v>
+        <v>697597</v>
       </c>
       <c r="R39" t="n">
-        <v>6556761</v>
+        <v>6556987</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5106,7 +5086,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5116,7 +5096,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5127,6 +5107,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5143,10 +5143,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122540885</v>
+        <v>122540898</v>
       </c>
       <c r="B40" t="n">
-        <v>95019</v>
+        <v>94972</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5159,34 +5159,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2170</v>
+        <v>210</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697628</v>
+        <v>697586</v>
       </c>
       <c r="R40" t="n">
-        <v>6556873</v>
+        <v>6556969</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5218,7 +5227,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5228,7 +5237,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5239,6 +5248,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5255,10 +5284,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122540898</v>
+        <v>122540885</v>
       </c>
       <c r="B41" t="n">
-        <v>94972</v>
+        <v>95019</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5271,43 +5300,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>210</v>
+        <v>2170</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>697586</v>
+        <v>697628</v>
       </c>
       <c r="R41" t="n">
-        <v>6556969</v>
+        <v>6556873</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5339,7 +5359,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5349,7 +5369,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5360,26 +5380,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540883</v>
+        <v>122540889</v>
       </c>
       <c r="B26" t="n">
-        <v>4776</v>
+        <v>110495</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,39 +3448,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697616</v>
+        <v>697668</v>
       </c>
       <c r="R26" t="n">
-        <v>6556904</v>
+        <v>6556773</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3512,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3522,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,26 +3528,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3569,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540887</v>
+        <v>122540883</v>
       </c>
       <c r="B27" t="n">
-        <v>110493</v>
+        <v>4776</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3585,34 +3560,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219711</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697678</v>
+        <v>697616</v>
       </c>
       <c r="R27" t="n">
-        <v>6556802</v>
+        <v>6556904</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3624,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3634,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,6 +3645,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3681,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540886</v>
+        <v>122540881</v>
       </c>
       <c r="B28" t="n">
-        <v>98377</v>
+        <v>94878</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3697,42 +3697,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219862</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697681</v>
+        <v>697597</v>
       </c>
       <c r="R28" t="n">
-        <v>6556807</v>
+        <v>6556987</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3761,7 +3756,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,7 +3766,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,6 +3777,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3798,10 +3813,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540897</v>
+        <v>122540886</v>
       </c>
       <c r="B29" t="n">
-        <v>94972</v>
+        <v>98379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3814,31 +3829,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>210</v>
+        <v>219862</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3847,10 +3858,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697581</v>
+        <v>697681</v>
       </c>
       <c r="R29" t="n">
-        <v>6556970</v>
+        <v>6556807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3882,7 +3893,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3892,7 +3903,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,26 +3914,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3942,7 +3933,7 @@
         <v>122540888</v>
       </c>
       <c r="B30" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4051,10 +4042,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540896</v>
+        <v>122540895</v>
       </c>
       <c r="B31" t="n">
-        <v>110493</v>
+        <v>57494</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4063,38 +4054,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697607</v>
+        <v>697710</v>
       </c>
       <c r="R31" t="n">
-        <v>6556976</v>
+        <v>6556732</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4126,7 +4122,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4136,7 +4132,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4163,10 +4164,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540891</v>
+        <v>122540896</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>110495</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4175,47 +4176,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697667</v>
+        <v>697607</v>
       </c>
       <c r="R32" t="n">
-        <v>6556761</v>
+        <v>6556976</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4247,7 +4239,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4257,7 +4249,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4284,10 +4276,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540893</v>
+        <v>122540891</v>
       </c>
       <c r="B33" t="n">
-        <v>100621</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4296,38 +4288,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697710</v>
+        <v>697667</v>
       </c>
       <c r="R33" t="n">
-        <v>6556732</v>
+        <v>6556761</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4359,7 +4360,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4369,7 +4370,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4396,10 +4397,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540890</v>
+        <v>122540897</v>
       </c>
       <c r="B34" t="n">
-        <v>110493</v>
+        <v>94974</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4412,34 +4413,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219711</v>
+        <v>210</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697667</v>
+        <v>697581</v>
       </c>
       <c r="R34" t="n">
-        <v>6556761</v>
+        <v>6556970</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4471,7 +4481,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4481,7 +4491,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4492,6 +4502,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4508,10 +4538,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122540878</v>
+        <v>122540893</v>
       </c>
       <c r="B35" t="n">
-        <v>8430</v>
+        <v>100623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4524,39 +4554,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697600</v>
+        <v>697710</v>
       </c>
       <c r="R35" t="n">
-        <v>6557016</v>
+        <v>6556732</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4588,7 +4613,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4598,7 +4623,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4609,26 +4634,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Betula # Barklös björklåga.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4645,10 +4650,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540889</v>
+        <v>122540890</v>
       </c>
       <c r="B36" t="n">
-        <v>110493</v>
+        <v>110495</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4685,10 +4690,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697668</v>
+        <v>697667</v>
       </c>
       <c r="R36" t="n">
-        <v>6556773</v>
+        <v>6556761</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4720,7 +4725,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4730,7 +4735,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4889,10 +4894,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122540895</v>
+        <v>122540878</v>
       </c>
       <c r="B38" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4901,31 +4906,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4934,10 +4939,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697710</v>
+        <v>697600</v>
       </c>
       <c r="R38" t="n">
-        <v>6556732</v>
+        <v>6557016</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4969,7 +4974,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4979,12 +4984,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4995,6 +4995,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5011,10 +5031,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540881</v>
+        <v>122540887</v>
       </c>
       <c r="B39" t="n">
-        <v>94876</v>
+        <v>110495</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5027,21 +5047,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>219711</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5051,13 +5071,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697597</v>
+        <v>697678</v>
       </c>
       <c r="R39" t="n">
-        <v>6556987</v>
+        <v>6556802</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5086,7 +5106,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5096,7 +5116,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5107,26 +5127,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5143,10 +5143,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122540898</v>
+        <v>122540885</v>
       </c>
       <c r="B40" t="n">
-        <v>94972</v>
+        <v>95021</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5159,43 +5159,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>210</v>
+        <v>2170</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697586</v>
+        <v>697628</v>
       </c>
       <c r="R40" t="n">
-        <v>6556969</v>
+        <v>6556873</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5227,7 +5218,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5237,7 +5228,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5248,26 +5239,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5284,10 +5255,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122540885</v>
+        <v>122540898</v>
       </c>
       <c r="B41" t="n">
-        <v>95019</v>
+        <v>94974</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5300,34 +5271,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2170</v>
+        <v>210</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>697628</v>
+        <v>697586</v>
       </c>
       <c r="R41" t="n">
-        <v>6556873</v>
+        <v>6556969</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5359,7 +5339,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5369,7 +5349,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5380,6 +5360,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5399,7 +5399,7 @@
         <v>122540882</v>
       </c>
       <c r="B42" t="n">
-        <v>96420</v>
+        <v>96422</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -4650,10 +4650,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540890</v>
+        <v>122540884</v>
       </c>
       <c r="B36" t="n">
-        <v>110495</v>
+        <v>8441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4666,34 +4666,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697667</v>
+        <v>697609</v>
       </c>
       <c r="R36" t="n">
-        <v>6556761</v>
+        <v>6556889</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4725,7 +4730,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4735,7 +4740,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4746,6 +4751,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4762,10 +4782,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540884</v>
+        <v>122540890</v>
       </c>
       <c r="B37" t="n">
-        <v>8441</v>
+        <v>110495</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4778,39 +4798,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697609</v>
+        <v>697667</v>
       </c>
       <c r="R37" t="n">
-        <v>6556889</v>
+        <v>6556761</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4842,7 +4857,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4852,7 +4867,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4863,21 +4878,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -4650,10 +4650,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540884</v>
+        <v>122540890</v>
       </c>
       <c r="B36" t="n">
-        <v>8441</v>
+        <v>110495</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4666,39 +4666,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697609</v>
+        <v>697667</v>
       </c>
       <c r="R36" t="n">
-        <v>6556889</v>
+        <v>6556761</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4730,7 +4725,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4740,7 +4735,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4751,21 +4746,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4782,10 +4762,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540890</v>
+        <v>122540884</v>
       </c>
       <c r="B37" t="n">
-        <v>110495</v>
+        <v>8441</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4798,34 +4778,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697667</v>
+        <v>697609</v>
       </c>
       <c r="R37" t="n">
-        <v>6556761</v>
+        <v>6556889</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4857,7 +4842,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4867,7 +4852,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4878,6 +4863,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -3432,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540889</v>
+        <v>122540891</v>
       </c>
       <c r="B26" t="n">
-        <v>110495</v>
+        <v>98357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3444,38 +3444,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697668</v>
+        <v>697667</v>
       </c>
       <c r="R26" t="n">
-        <v>6556773</v>
+        <v>6556761</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3516,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3526,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540883</v>
+        <v>122540886</v>
       </c>
       <c r="B27" t="n">
-        <v>4776</v>
+        <v>98379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3560,27 +3569,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3589,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697616</v>
+        <v>697681</v>
       </c>
       <c r="R27" t="n">
-        <v>6556904</v>
+        <v>6556807</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3624,7 +3633,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3634,7 +3643,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,26 +3654,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3681,10 +3670,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540881</v>
+        <v>122540889</v>
       </c>
       <c r="B28" t="n">
-        <v>94878</v>
+        <v>110495</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3697,21 +3686,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3721,13 +3710,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697597</v>
+        <v>697668</v>
       </c>
       <c r="R28" t="n">
-        <v>6556987</v>
+        <v>6556773</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3756,7 +3745,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3766,7 +3755,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3777,26 +3766,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3813,10 +3782,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540886</v>
+        <v>122540888</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>100623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3829,39 +3798,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697681</v>
+        <v>697678</v>
       </c>
       <c r="R29" t="n">
-        <v>6556807</v>
+        <v>6556802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3893,7 +3857,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3903,7 +3867,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3930,10 +3894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122540888</v>
+        <v>122540890</v>
       </c>
       <c r="B30" t="n">
-        <v>100623</v>
+        <v>110495</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3946,21 +3910,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3970,10 +3934,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697678</v>
+        <v>697667</v>
       </c>
       <c r="R30" t="n">
-        <v>6556802</v>
+        <v>6556761</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4005,7 +3969,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4015,7 +3979,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4042,10 +4006,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122540895</v>
+        <v>122540881</v>
       </c>
       <c r="B31" t="n">
-        <v>57494</v>
+        <v>94878</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4054,46 +4018,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697710</v>
+        <v>697597</v>
       </c>
       <c r="R31" t="n">
-        <v>6556732</v>
+        <v>6556987</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4122,7 +4081,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4132,12 +4091,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,6 +4102,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies # Fuktig granlåga som låg över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4164,10 +4138,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122540896</v>
+        <v>122540883</v>
       </c>
       <c r="B32" t="n">
-        <v>110495</v>
+        <v>4776</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4180,34 +4154,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219711</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697607</v>
+        <v>697616</v>
       </c>
       <c r="R32" t="n">
-        <v>6556976</v>
+        <v>6556904</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4239,7 +4218,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4249,7 +4228,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,6 +4239,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4276,10 +4275,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122540891</v>
+        <v>122540897</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>94974</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4288,35 +4287,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4325,10 +4324,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697667</v>
+        <v>697581</v>
       </c>
       <c r="R33" t="n">
-        <v>6556761</v>
+        <v>6556970</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4360,7 +4359,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4370,7 +4369,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4381,6 +4380,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Tallågor i stockbro över skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4397,10 +4416,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122540897</v>
+        <v>122540896</v>
       </c>
       <c r="B34" t="n">
-        <v>94974</v>
+        <v>110495</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4413,43 +4432,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697581</v>
+        <v>697607</v>
       </c>
       <c r="R34" t="n">
-        <v>6556970</v>
+        <v>6556976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4481,7 +4491,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4491,7 +4501,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4502,26 +4512,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Tallågor i stockbro över skogsbäck.</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallågor i stockbro över skogsbäck.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4650,10 +4640,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122540884</v>
+        <v>122540887</v>
       </c>
       <c r="B36" t="n">
-        <v>8441</v>
+        <v>110495</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4666,39 +4656,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697609</v>
+        <v>697678</v>
       </c>
       <c r="R36" t="n">
-        <v>6556889</v>
+        <v>6556802</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4730,7 +4715,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4740,7 +4725,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4751,21 +4736,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4782,10 +4752,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122540890</v>
+        <v>122540895</v>
       </c>
       <c r="B37" t="n">
-        <v>110495</v>
+        <v>57494</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4794,38 +4764,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697667</v>
+        <v>697710</v>
       </c>
       <c r="R37" t="n">
-        <v>6556761</v>
+        <v>6556732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4857,7 +4832,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4867,7 +4842,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5031,10 +5011,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122540887</v>
+        <v>122540884</v>
       </c>
       <c r="B39" t="n">
-        <v>110495</v>
+        <v>8441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5047,34 +5027,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697678</v>
+        <v>697609</v>
       </c>
       <c r="R39" t="n">
-        <v>6556802</v>
+        <v>6556889</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5106,7 +5091,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5116,7 +5101,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5127,6 +5112,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -5399,7 +5399,7 @@
         <v>122540882</v>
       </c>
       <c r="B42" t="n">
-        <v>96422</v>
+        <v>96430</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5531,6 +5531,242 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124203365</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97996</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sandtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>697639</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6556734</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124203335</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97996</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sandtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>697640</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6556732</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -5533,7 +5533,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124203335</v>
+        <v>124203365</v>
       </c>
       <c r="B43" t="n">
         <v>98018</v>
@@ -5566,11 +5566,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -5581,13 +5577,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697640</v>
+        <v>697639</v>
       </c>
       <c r="R43" t="n">
-        <v>6556732</v>
+        <v>6556734</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5616,7 +5612,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5626,7 +5622,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5653,7 +5649,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124203365</v>
+        <v>124203335</v>
       </c>
       <c r="B44" t="n">
         <v>98018</v>
@@ -5686,7 +5682,11 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697639</v>
+        <v>697640</v>
       </c>
       <c r="R44" t="n">
-        <v>6556734</v>
+        <v>6556732</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 2228-2025 artfynd.xlsx
+++ b/artfynd/A 2228-2025 artfynd.xlsx
@@ -5533,7 +5533,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124203365</v>
+        <v>124203335</v>
       </c>
       <c r="B43" t="n">
         <v>98018</v>
@@ -5566,7 +5566,11 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -5577,13 +5581,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697639</v>
+        <v>697640</v>
       </c>
       <c r="R43" t="n">
-        <v>6556734</v>
+        <v>6556732</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5612,7 +5616,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5622,7 +5626,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5649,7 +5653,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124203335</v>
+        <v>124203365</v>
       </c>
       <c r="B44" t="n">
         <v>98018</v>
@@ -5682,11 +5686,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697640</v>
+        <v>697639</v>
       </c>
       <c r="R44" t="n">
-        <v>6556732</v>
+        <v>6556734</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
